--- a/Excel/Day 09/Excel-Practice-(Day-09).xlsx
+++ b/Excel/Day 09/Excel-Practice-(Day-09).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analyst\Excel\Day 09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B997752C-02E4-4ACE-9D54-096F5139BE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD492517-8D0B-45A6-86F7-8FD18781B252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11835" tabRatio="678" firstSheet="17" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11835" tabRatio="678" firstSheet="17" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
@@ -3326,9 +3326,9 @@
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="&quot;Rs. &quot;#,##0"/>
     <numFmt numFmtId="168" formatCode="&quot;Rs.&quot;\ #,##0"/>
-    <numFmt numFmtId="176" formatCode="dd\-mm\-yyyy"/>
-    <numFmt numFmtId="177" formatCode="dd"/>
-    <numFmt numFmtId="181" formatCode="mm\-dd\-yyyy"/>
+    <numFmt numFmtId="169" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="170" formatCode="dd"/>
+    <numFmt numFmtId="171" formatCode="mm\-dd\-yyyy"/>
   </numFmts>
   <fonts count="32" x14ac:knownFonts="1">
     <font>
@@ -5362,6 +5362,168 @@
     <xf numFmtId="0" fontId="28" fillId="5" borderId="63" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="37" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="37" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="18" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="40" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="40" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="41" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="42" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5449,36 +5611,8 @@
     <xf numFmtId="0" fontId="22" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5488,140 +5622,6 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="35" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="39" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="37" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="37" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="18" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="40" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="0" fillId="40" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="41" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="42" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5646,152 +5646,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="4" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6597,6 +6451,152 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="4" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -7530,15 +7530,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2688C5AF-1E0A-4EDD-AF11-5A4BBABB9721}" name="Employees" displayName="Employees" ref="A1:F39" totalsRowCount="1" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2688C5AF-1E0A-4EDD-AF11-5A4BBABB9721}" name="Employees" displayName="Employees" ref="A1:F39" totalsRowCount="1" headerRowDxfId="45" dataDxfId="43" headerRowBorderDxfId="44" tableBorderDxfId="42">
   <autoFilter ref="A1:F38" xr:uid="{2688C5AF-1E0A-4EDD-AF11-5A4BBABB9721}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{B1033A5F-C26D-48E8-B4BE-5F7761A770FB}" name="Date" dataDxfId="55" totalsRowDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{AD6BA12D-25CE-4D3E-8E2A-1DD281A3FDA5}" name="Employee Name" dataDxfId="53" totalsRowDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{96E1CF2B-482C-42D2-8CEA-C0CE6D69979C}" name="Department" dataDxfId="51" totalsRowDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{602E6D48-4D10-4D1E-9636-6A41FF0A4753}" name="Region" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{98D904BD-DEE8-4674-A97B-995E27B5AB23}" name="Sales (Rs.)" dataDxfId="47" totalsRowDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{F7A5EC06-42D8-4DD0-83BA-C91339988D38}" name="Target (Rs.)" totalsRowFunction="custom" dataDxfId="45" totalsRowDxfId="44">
+    <tableColumn id="1" xr3:uid="{B1033A5F-C26D-48E8-B4BE-5F7761A770FB}" name="Date" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{AD6BA12D-25CE-4D3E-8E2A-1DD281A3FDA5}" name="Employee Name" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{96E1CF2B-482C-42D2-8CEA-C0CE6D69979C}" name="Department" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{602E6D48-4D10-4D1E-9636-6A41FF0A4753}" name="Region" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{98D904BD-DEE8-4674-A97B-995E27B5AB23}" name="Sales (Rs.)" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{F7A5EC06-42D8-4DD0-83BA-C91339988D38}" name="Target (Rs.)" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="30">
       <totalsRowFormula>SUM(F2:F38)</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -20258,22 +20258,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:29" x14ac:dyDescent="0.25">
-      <c r="D1" s="244" t="s">
+      <c r="D1" s="302" t="s">
         <v>541</v>
       </c>
-      <c r="E1" s="245"/>
-      <c r="F1" s="245"/>
-      <c r="G1" s="245"/>
-      <c r="H1" s="245"/>
-      <c r="I1" s="245"/>
-      <c r="X1" s="246" t="s">
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="303"/>
+      <c r="X1" s="304" t="s">
         <v>542</v>
       </c>
-      <c r="Y1" s="247"/>
-      <c r="Z1" s="247"/>
-      <c r="AA1" s="247"/>
-      <c r="AB1" s="247"/>
-      <c r="AC1" s="248"/>
+      <c r="Y1" s="305"/>
+      <c r="Z1" s="305"/>
+      <c r="AA1" s="305"/>
+      <c r="AB1" s="305"/>
+      <c r="AC1" s="306"/>
     </row>
     <row r="2" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D2" s="106" t="s">
@@ -20294,29 +20294,29 @@
       <c r="I2" s="106" t="s">
         <v>537</v>
       </c>
-      <c r="K2" s="246" t="s">
+      <c r="K2" s="304" t="s">
         <v>543</v>
       </c>
-      <c r="L2" s="247"/>
-      <c r="M2" s="247"/>
-      <c r="N2" s="247"/>
-      <c r="O2" s="247"/>
-      <c r="P2" s="247"/>
-      <c r="Q2" s="247"/>
-      <c r="R2" s="247"/>
-      <c r="S2" s="247"/>
-      <c r="T2" s="247"/>
-      <c r="U2" s="247"/>
-      <c r="V2" s="248"/>
-      <c r="X2" s="244" t="str">
+      <c r="L2" s="305"/>
+      <c r="M2" s="305"/>
+      <c r="N2" s="305"/>
+      <c r="O2" s="305"/>
+      <c r="P2" s="305"/>
+      <c r="Q2" s="305"/>
+      <c r="R2" s="305"/>
+      <c r="S2" s="305"/>
+      <c r="T2" s="305"/>
+      <c r="U2" s="305"/>
+      <c r="V2" s="306"/>
+      <c r="X2" s="302" t="str">
         <f t="shared" ref="X2:X17" si="0">D1</f>
         <v>OPERATIONS</v>
       </c>
-      <c r="Y2" s="245"/>
-      <c r="Z2" s="245"/>
-      <c r="AA2" s="245"/>
-      <c r="AB2" s="245"/>
-      <c r="AC2" s="245"/>
+      <c r="Y2" s="303"/>
+      <c r="Z2" s="303"/>
+      <c r="AA2" s="303"/>
+      <c r="AB2" s="303"/>
+      <c r="AC2" s="303"/>
     </row>
     <row r="3" spans="4:29" x14ac:dyDescent="0.25">
       <c r="D3" s="105" t="s">
@@ -20333,7 +20333,7 @@
       </c>
       <c r="H3" s="135">
         <f t="shared" ref="H3:H16" ca="1" si="1">(RANDBETWEEN(10,50))/100</f>
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="I3" s="105">
         <v>100</v>
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H4" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="X4" s="105" t="str">
         <f t="shared" si="0"/>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="AB4" s="135">
         <f t="shared" ca="1" si="2"/>
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="AC4" s="105">
         <f t="shared" si="2"/>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="H5" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="X5" s="105" t="str">
         <f t="shared" si="0"/>
@@ -20440,7 +20440,7 @@
       </c>
       <c r="AB5" s="135">
         <f t="shared" ref="AB5:AB17" ca="1" si="6">H4</f>
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="6" spans="4:29" x14ac:dyDescent="0.25">
@@ -20458,20 +20458,20 @@
       </c>
       <c r="H6" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.26</v>
-      </c>
-      <c r="L6" s="246" t="s">
+        <v>0.45</v>
+      </c>
+      <c r="L6" s="304" t="s">
         <v>540</v>
       </c>
-      <c r="M6" s="247"/>
-      <c r="N6" s="247"/>
-      <c r="O6" s="247"/>
-      <c r="P6" s="247"/>
-      <c r="Q6" s="247"/>
-      <c r="R6" s="247"/>
-      <c r="S6" s="247"/>
-      <c r="T6" s="247"/>
-      <c r="U6" s="248"/>
+      <c r="M6" s="305"/>
+      <c r="N6" s="305"/>
+      <c r="O6" s="305"/>
+      <c r="P6" s="305"/>
+      <c r="Q6" s="305"/>
+      <c r="R6" s="305"/>
+      <c r="S6" s="305"/>
+      <c r="T6" s="305"/>
+      <c r="U6" s="306"/>
       <c r="X6" s="105" t="str">
         <f t="shared" si="0"/>
         <v>Muhammad Hamza</v>
@@ -20490,7 +20490,7 @@
       </c>
       <c r="AB6" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="7" spans="4:29" x14ac:dyDescent="0.25">
@@ -20508,7 +20508,7 @@
       </c>
       <c r="H7" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.46</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="X7" s="105" t="str">
         <f t="shared" si="0"/>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="AB7" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.26</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="8" spans="4:29" x14ac:dyDescent="0.25">
@@ -20546,7 +20546,7 @@
       </c>
       <c r="H8" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="M8" s="105">
         <v>137196</v>
@@ -20572,7 +20572,7 @@
       </c>
       <c r="AB8" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.46</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="9" spans="4:29" x14ac:dyDescent="0.25">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="H9" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="M9" s="105">
         <v>64256</v>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AB9" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="10" spans="4:29" x14ac:dyDescent="0.25">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="H10" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="M10" s="105">
         <v>137080</v>
@@ -20658,7 +20658,7 @@
       </c>
       <c r="AB10" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" spans="4:29" x14ac:dyDescent="0.25">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="H11" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="M11" s="105">
         <v>95302</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="AB11" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" spans="4:29" x14ac:dyDescent="0.25">
@@ -20720,7 +20720,7 @@
       </c>
       <c r="H12" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.49</v>
+        <v>0.18</v>
       </c>
       <c r="M12" s="105">
         <v>68657</v>
@@ -20746,7 +20746,7 @@
       </c>
       <c r="AB12" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="13" spans="4:29" x14ac:dyDescent="0.25">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="H13" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.28000000000000003</v>
+        <v>0.11</v>
       </c>
       <c r="M13" s="105">
         <v>66062</v>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="AB13" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.49</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="14" spans="4:29" x14ac:dyDescent="0.25">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="H14" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="M14" s="105">
         <v>98878</v>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="AB14" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.28000000000000003</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="15" spans="4:29" x14ac:dyDescent="0.25">
@@ -20852,7 +20852,7 @@
       </c>
       <c r="H15" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="M15" s="105">
         <v>40851</v>
@@ -20878,7 +20878,7 @@
       </c>
       <c r="AB15" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" spans="4:29" x14ac:dyDescent="0.25">
@@ -20896,7 +20896,7 @@
       </c>
       <c r="H16" s="135">
         <f t="shared" ca="1" si="1"/>
-        <v>0.39</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M16" s="105"/>
       <c r="N16" s="105"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="AB16" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="17" spans="4:28" x14ac:dyDescent="0.25">
@@ -20947,7 +20947,7 @@
       </c>
       <c r="AB17" s="135">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="18" spans="4:28" x14ac:dyDescent="0.25">
@@ -20995,31 +20995,31 @@
       </c>
     </row>
     <row r="29" spans="4:28" x14ac:dyDescent="0.25">
-      <c r="D29" s="245" t="s">
+      <c r="D29" s="303" t="s">
         <v>538</v>
       </c>
-      <c r="E29" s="245"/>
-      <c r="F29" s="245"/>
-      <c r="G29" s="245"/>
-      <c r="H29" s="245"/>
-      <c r="I29" s="245"/>
-      <c r="J29" s="245"/>
-      <c r="K29" s="245"/>
-      <c r="L29" s="245"/>
-      <c r="M29" s="245"/>
-      <c r="N29" s="245"/>
-      <c r="O29" s="245"/>
-      <c r="P29" s="245"/>
-      <c r="Q29" s="245"/>
-      <c r="R29" s="245"/>
-      <c r="U29" s="246" t="s">
+      <c r="E29" s="303"/>
+      <c r="F29" s="303"/>
+      <c r="G29" s="303"/>
+      <c r="H29" s="303"/>
+      <c r="I29" s="303"/>
+      <c r="J29" s="303"/>
+      <c r="K29" s="303"/>
+      <c r="L29" s="303"/>
+      <c r="M29" s="303"/>
+      <c r="N29" s="303"/>
+      <c r="O29" s="303"/>
+      <c r="P29" s="303"/>
+      <c r="Q29" s="303"/>
+      <c r="R29" s="303"/>
+      <c r="U29" s="304" t="s">
         <v>539</v>
       </c>
-      <c r="V29" s="247"/>
-      <c r="W29" s="247"/>
-      <c r="X29" s="247"/>
-      <c r="Y29" s="247"/>
-      <c r="Z29" s="248"/>
+      <c r="V29" s="305"/>
+      <c r="W29" s="305"/>
+      <c r="X29" s="305"/>
+      <c r="Y29" s="305"/>
+      <c r="Z29" s="306"/>
     </row>
     <row r="30" spans="4:28" x14ac:dyDescent="0.25">
       <c r="D30" s="106" t="s">
@@ -21563,38 +21563,38 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="249" t="s">
+      <c r="A4" s="307" t="s">
         <v>545</v>
       </c>
-      <c r="B4" s="250"/>
-      <c r="C4" s="250"/>
-      <c r="D4" s="250"/>
-      <c r="E4" s="250"/>
-      <c r="F4" s="250"/>
-      <c r="H4" s="249" t="s">
+      <c r="B4" s="308"/>
+      <c r="C4" s="308"/>
+      <c r="D4" s="308"/>
+      <c r="E4" s="308"/>
+      <c r="F4" s="308"/>
+      <c r="H4" s="307" t="s">
         <v>546</v>
       </c>
-      <c r="I4" s="250"/>
-      <c r="J4" s="250"/>
-      <c r="K4" s="250"/>
-      <c r="L4" s="250"/>
-      <c r="M4" s="250"/>
-      <c r="P4" s="249" t="s">
+      <c r="I4" s="308"/>
+      <c r="J4" s="308"/>
+      <c r="K4" s="308"/>
+      <c r="L4" s="308"/>
+      <c r="M4" s="308"/>
+      <c r="P4" s="307" t="s">
         <v>548</v>
       </c>
-      <c r="Q4" s="250"/>
-      <c r="R4" s="250"/>
-      <c r="S4" s="250"/>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="W4" s="249" t="s">
+      <c r="Q4" s="308"/>
+      <c r="R4" s="308"/>
+      <c r="S4" s="308"/>
+      <c r="T4" s="308"/>
+      <c r="U4" s="308"/>
+      <c r="W4" s="307" t="s">
         <v>547</v>
       </c>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
-      <c r="AA4" s="250"/>
-      <c r="AB4" s="250"/>
+      <c r="X4" s="308"/>
+      <c r="Y4" s="308"/>
+      <c r="Z4" s="308"/>
+      <c r="AA4" s="308"/>
+      <c r="AB4" s="308"/>
     </row>
     <row r="5" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
@@ -24063,22 +24063,22 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="251" t="s">
+      <c r="B3" s="309" t="s">
         <v>553</v>
       </c>
-      <c r="C3" s="251"/>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="252">
+      <c r="C3" s="309"/>
+      <c r="D3" s="309"/>
+      <c r="E3" s="309"/>
+      <c r="F3" s="309"/>
+      <c r="G3" s="310">
         <v>400</v>
       </c>
-      <c r="H3" s="252"/>
-      <c r="I3" s="252"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="252"/>
-      <c r="L3" s="252"/>
-      <c r="M3" s="252"/>
+      <c r="H3" s="310"/>
+      <c r="I3" s="310"/>
+      <c r="J3" s="310"/>
+      <c r="K3" s="310"/>
+      <c r="L3" s="310"/>
+      <c r="M3" s="310"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="137" t="s">
@@ -24779,18 +24779,18 @@
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B25" s="251" t="s">
+      <c r="B25" s="309" t="s">
         <v>553</v>
       </c>
-      <c r="C25" s="251"/>
-      <c r="D25" s="251"/>
-      <c r="E25" s="251"/>
-      <c r="F25" s="251"/>
-      <c r="G25" s="253">
+      <c r="C25" s="309"/>
+      <c r="D25" s="309"/>
+      <c r="E25" s="309"/>
+      <c r="F25" s="309"/>
+      <c r="G25" s="311">
         <v>400</v>
       </c>
-      <c r="H25" s="254"/>
-      <c r="I25" s="254"/>
+      <c r="H25" s="312"/>
+      <c r="I25" s="312"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B26" s="137" t="s">
@@ -25684,17 +25684,17 @@
       </c>
     </row>
     <row r="24" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="255" t="s">
+      <c r="B24" s="313" t="s">
         <v>734</v>
       </c>
-      <c r="C24" s="256"/>
-      <c r="D24" s="256"/>
-      <c r="E24" s="256"/>
-      <c r="F24" s="256"/>
-      <c r="G24" s="257"/>
+      <c r="C24" s="314"/>
+      <c r="D24" s="314"/>
+      <c r="E24" s="314"/>
+      <c r="F24" s="314"/>
+      <c r="G24" s="315"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="G31" s="268"/>
+      <c r="G31" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -25736,19 +25736,19 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="258" t="s">
+      <c r="B2" s="316" t="s">
         <v>564</v>
       </c>
-      <c r="C2" s="259"/>
+      <c r="C2" s="317"/>
       <c r="D2" s="145"/>
-      <c r="E2" s="258" t="s">
+      <c r="E2" s="316" t="s">
         <v>568</v>
       </c>
-      <c r="F2" s="259"/>
-      <c r="H2" s="258" t="s">
+      <c r="F2" s="317"/>
+      <c r="H2" s="316" t="s">
         <v>572</v>
       </c>
-      <c r="I2" s="259"/>
+      <c r="I2" s="317"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="148" t="s">
@@ -25989,14 +25989,14 @@
     </row>
     <row r="15" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="258" t="s">
+      <c r="B16" s="316" t="s">
         <v>687</v>
       </c>
-      <c r="C16" s="259"/>
-      <c r="E16" s="258" t="s">
+      <c r="C16" s="317"/>
+      <c r="E16" s="316" t="s">
         <v>580</v>
       </c>
-      <c r="F16" s="259"/>
+      <c r="F16" s="317"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="148" t="s">
@@ -26154,18 +26154,18 @@
     </row>
     <row r="31" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="258" t="s">
+      <c r="B32" s="316" t="s">
         <v>588</v>
       </c>
-      <c r="C32" s="259"/>
-      <c r="E32" s="258" t="s">
+      <c r="C32" s="317"/>
+      <c r="E32" s="316" t="s">
         <v>584</v>
       </c>
-      <c r="F32" s="259"/>
-      <c r="H32" s="258" t="s">
+      <c r="F32" s="317"/>
+      <c r="H32" s="316" t="s">
         <v>592</v>
       </c>
-      <c r="I32" s="259"/>
+      <c r="I32" s="317"/>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B33" s="148" t="s">
@@ -26395,39 +26395,39 @@
       </c>
     </row>
     <row r="45" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="260" t="s">
+      <c r="B45" s="318" t="s">
         <v>732</v>
       </c>
-      <c r="C45" s="260"/>
-      <c r="D45" s="260"/>
+      <c r="C45" s="318"/>
+      <c r="D45" s="318"/>
       <c r="E45" s="170"/>
       <c r="F45" s="170"/>
-      <c r="G45" s="260" t="s">
+      <c r="G45" s="318" t="s">
         <v>719</v>
       </c>
-      <c r="H45" s="260"/>
-      <c r="I45" s="260"/>
+      <c r="H45" s="318"/>
+      <c r="I45" s="318"/>
       <c r="J45" s="170"/>
-      <c r="K45" s="260" t="s">
+      <c r="K45" s="318" t="s">
         <v>707</v>
       </c>
-      <c r="L45" s="260"/>
-      <c r="M45" s="260"/>
-      <c r="O45" s="260" t="s">
+      <c r="L45" s="318"/>
+      <c r="M45" s="318"/>
+      <c r="O45" s="318" t="s">
         <v>730</v>
       </c>
-      <c r="P45" s="260"/>
-      <c r="Q45" s="260"/>
-      <c r="S45" s="260" t="s">
+      <c r="P45" s="318"/>
+      <c r="Q45" s="318"/>
+      <c r="S45" s="318" t="s">
         <v>731</v>
       </c>
-      <c r="T45" s="260"/>
-      <c r="U45" s="260"/>
-      <c r="W45" s="260" t="s">
+      <c r="T45" s="318"/>
+      <c r="U45" s="318"/>
+      <c r="W45" s="318" t="s">
         <v>733</v>
       </c>
-      <c r="X45" s="260"/>
-      <c r="Y45" s="260"/>
+      <c r="X45" s="318"/>
+      <c r="Y45" s="318"/>
     </row>
     <row r="46" spans="2:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="167" t="s">
@@ -27114,11 +27114,11 @@
       <c r="D59" s="170"/>
       <c r="E59" s="170"/>
       <c r="F59" s="170"/>
-      <c r="G59" s="260" t="s">
+      <c r="G59" s="318" t="s">
         <v>735</v>
       </c>
-      <c r="H59" s="260"/>
-      <c r="I59" s="260"/>
+      <c r="H59" s="318"/>
+      <c r="I59" s="318"/>
       <c r="J59" s="170"/>
       <c r="K59" s="170"/>
       <c r="L59" s="170"/>
@@ -27225,22 +27225,22 @@
     </row>
     <row r="74" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="75" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B75" s="258" t="s">
+      <c r="B75" s="316" t="s">
         <v>738</v>
       </c>
-      <c r="C75" s="259"/>
-      <c r="E75" s="258" t="s">
+      <c r="C75" s="317"/>
+      <c r="E75" s="316" t="s">
         <v>741</v>
       </c>
-      <c r="F75" s="259"/>
-      <c r="H75" s="258" t="s">
+      <c r="F75" s="317"/>
+      <c r="H75" s="316" t="s">
         <v>740</v>
       </c>
-      <c r="I75" s="259"/>
-      <c r="K75" s="258" t="s">
+      <c r="I75" s="317"/>
+      <c r="K75" s="316" t="s">
         <v>742</v>
       </c>
-      <c r="L75" s="259"/>
+      <c r="L75" s="317"/>
     </row>
     <row r="76" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B76" s="148" t="s">
@@ -27540,10 +27540,10 @@
     </row>
     <row r="89" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="90" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="258" t="s">
+      <c r="B90" s="316" t="s">
         <v>628</v>
       </c>
-      <c r="C90" s="259"/>
+      <c r="C90" s="317"/>
     </row>
     <row r="91" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B91" s="148" t="s">
@@ -27555,14 +27555,14 @@
       <c r="D91" s="148" t="s">
         <v>745</v>
       </c>
-      <c r="F91" s="258" t="s">
+      <c r="F91" s="316" t="s">
         <v>746</v>
       </c>
-      <c r="G91" s="259"/>
-      <c r="I91" s="258" t="s">
+      <c r="G91" s="317"/>
+      <c r="I91" s="316" t="s">
         <v>748</v>
       </c>
-      <c r="J91" s="259"/>
+      <c r="J91" s="317"/>
     </row>
     <row r="92" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B92" s="183">
@@ -27655,14 +27655,14 @@
         <f t="shared" si="17"/>
         <v>October</v>
       </c>
-      <c r="F97" s="258" t="s">
+      <c r="F97" s="316" t="s">
         <v>637</v>
       </c>
-      <c r="G97" s="259"/>
-      <c r="I97" s="258" t="s">
+      <c r="G97" s="317"/>
+      <c r="I97" s="316" t="s">
         <v>641</v>
       </c>
-      <c r="J97" s="259"/>
+      <c r="J97" s="317"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="183">
@@ -27719,6 +27719,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="E16:F16"/>
     <mergeCell ref="F97:G97"/>
     <mergeCell ref="I97:J97"/>
     <mergeCell ref="W45:Y45"/>
@@ -27735,14 +27743,6 @@
     <mergeCell ref="B75:C75"/>
     <mergeCell ref="E75:F75"/>
     <mergeCell ref="K75:L75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="E16:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -28385,14 +28385,14 @@
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="261" t="s">
+      <c r="B34" s="319" t="s">
         <v>898</v>
       </c>
-      <c r="C34" s="262"/>
-      <c r="D34" s="262"/>
-      <c r="E34" s="262"/>
-      <c r="F34" s="262"/>
-      <c r="G34" s="263"/>
+      <c r="C34" s="320"/>
+      <c r="D34" s="320"/>
+      <c r="E34" s="320"/>
+      <c r="F34" s="320"/>
+      <c r="G34" s="321"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -28428,29 +28428,29 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="264" t="s">
+      <c r="B3" s="322" t="s">
         <v>899</v>
       </c>
-      <c r="C3" s="264"/>
-      <c r="D3" s="264"/>
-      <c r="F3" s="260" t="s">
+      <c r="C3" s="322"/>
+      <c r="D3" s="322"/>
+      <c r="F3" s="318" t="s">
         <v>828</v>
       </c>
-      <c r="G3" s="260"/>
-      <c r="H3" s="260"/>
+      <c r="G3" s="318"/>
+      <c r="H3" s="318"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="209">
         <f t="shared" ref="B4:D13" ca="1" si="0">RAND()</f>
-        <v>0.99392438445869646</v>
+        <v>0.90733738150419418</v>
       </c>
       <c r="C4" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.62101835470636302</v>
+        <v>0.26667343928159193</v>
       </c>
       <c r="D4" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.76635422317842994</v>
+        <v>0.42420841465343551</v>
       </c>
       <c r="F4" s="167" t="s">
         <v>901</v>
@@ -28465,15 +28465,15 @@
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" s="209">
         <f t="shared" ca="1" si="0"/>
-        <v>0.55141020112104444</v>
+        <v>0.85360980392318497</v>
       </c>
       <c r="C5" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.37801974580999398</v>
+        <v>7.0159966880617652E-2</v>
       </c>
       <c r="D5" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.96566191863858652</v>
+        <v>0.23576068936276218</v>
       </c>
       <c r="F5" s="169">
         <v>1</v>
@@ -28489,15 +28489,15 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" s="209">
         <f t="shared" ca="1" si="0"/>
-        <v>0.19490505608623854</v>
+        <v>0.44973813106691529</v>
       </c>
       <c r="C6" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.37860528117252912</v>
+        <v>0.49718414493319385</v>
       </c>
       <c r="D6" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.21084433279021542</v>
+        <v>0.54575618753162458</v>
       </c>
       <c r="F6" s="169">
         <v>2</v>
@@ -28513,15 +28513,15 @@
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="209">
         <f t="shared" ca="1" si="0"/>
-        <v>0.55721331595149659</v>
+        <v>0.54676362259211564</v>
       </c>
       <c r="C7" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.56582127500515256</v>
+        <v>0.6487928514838267</v>
       </c>
       <c r="D7" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.58295782273770924</v>
+        <v>5.5382871446860715E-2</v>
       </c>
       <c r="F7" s="169">
         <v>3</v>
@@ -28537,15 +28537,15 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" s="209">
         <f t="shared" ca="1" si="0"/>
-        <v>0.66682948030652622</v>
+        <v>0.69131945111443815</v>
       </c>
       <c r="C8" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.16329516748909334</v>
+        <v>0.76546409983552899</v>
       </c>
       <c r="D8" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.64010320872719817</v>
+        <v>0.55965483466662369</v>
       </c>
       <c r="F8" s="169">
         <v>4</v>
@@ -28561,15 +28561,15 @@
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="209">
         <f t="shared" ca="1" si="0"/>
-        <v>0.43028925344126168</v>
+        <v>9.5696812146230936E-2</v>
       </c>
       <c r="C9" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.370507613743008</v>
+        <v>0.44177462544021351</v>
       </c>
       <c r="D9" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>3.3258268251797785E-2</v>
+        <v>0.34537159683454455</v>
       </c>
       <c r="F9" s="169">
         <v>5</v>
@@ -28585,15 +28585,15 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="209">
         <f t="shared" ca="1" si="0"/>
-        <v>0.70282234460078008</v>
+        <v>5.2778960117548568E-2</v>
       </c>
       <c r="C10" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.96216425703924657</v>
+        <v>0.69912943767110414</v>
       </c>
       <c r="D10" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.61193170414084863</v>
+        <v>0.94797332638881704</v>
       </c>
       <c r="F10" s="169">
         <v>6</v>
@@ -28609,15 +28609,15 @@
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="209">
         <f t="shared" ca="1" si="0"/>
-        <v>0.27824640518536015</v>
+        <v>0.30181589053520297</v>
       </c>
       <c r="C11" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.38801560570532823</v>
+        <v>4.281711115754061E-2</v>
       </c>
       <c r="D11" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.4798850101790697</v>
+        <v>0.30670539388062401</v>
       </c>
       <c r="F11" s="169">
         <v>7</v>
@@ -28633,15 +28633,15 @@
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="209">
         <f t="shared" ca="1" si="0"/>
-        <v>0.78297731828992556</v>
+        <v>0.49511855298678586</v>
       </c>
       <c r="C12" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.44073820626916216</v>
+        <v>0.25808519035760669</v>
       </c>
       <c r="D12" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.7087512052263738</v>
+        <v>2.4018537539440832E-3</v>
       </c>
       <c r="F12" s="169">
         <v>8</v>
@@ -28657,15 +28657,15 @@
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" s="209">
         <f t="shared" ca="1" si="0"/>
-        <v>0.12784980508140287</v>
+        <v>0.82247504928590354</v>
       </c>
       <c r="C13" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.10512348983856157</v>
+        <v>0.47730723351501381</v>
       </c>
       <c r="D13" s="168">
         <f t="shared" ca="1" si="0"/>
-        <v>0.84891652830233999</v>
+        <v>0.94135405220457757</v>
       </c>
       <c r="F13" s="169">
         <v>9</v>
@@ -28691,35 +28691,35 @@
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="266" t="s">
+      <c r="B17" s="323" t="s">
         <v>900</v>
       </c>
-      <c r="C17" s="264"/>
-      <c r="D17" s="264"/>
-      <c r="F17" s="260" t="s">
+      <c r="C17" s="322"/>
+      <c r="D17" s="322"/>
+      <c r="F17" s="318" t="s">
         <v>903</v>
       </c>
-      <c r="G17" s="260"/>
-      <c r="H17" s="260"/>
-      <c r="J17" s="260" t="s">
+      <c r="G17" s="318"/>
+      <c r="H17" s="318"/>
+      <c r="J17" s="318" t="s">
         <v>906</v>
       </c>
-      <c r="K17" s="260"/>
-      <c r="L17" s="260"/>
-      <c r="M17" s="260"/>
+      <c r="K17" s="318"/>
+      <c r="L17" s="318"/>
+      <c r="M17" s="318"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="209">
         <f ca="1">RANDBETWEEN(0,100)</f>
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="C18" s="168">
         <f t="shared" ref="B18:D27" ca="1" si="2">RANDBETWEEN(0,100)</f>
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="D18" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F18" s="167" t="s">
         <v>901</v>
@@ -28746,15 +28746,15 @@
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="C19" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="D19" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="F19" s="169">
         <v>1</v>
@@ -28784,15 +28784,15 @@
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="C20" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="D20" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F20" s="169">
         <v>2</v>
@@ -28822,15 +28822,15 @@
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C21" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="D21" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F21" s="169">
         <v>3</v>
@@ -28860,15 +28860,15 @@
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C22" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D22" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="F22" s="169">
         <v>4</v>
@@ -28898,15 +28898,15 @@
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C23" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D23" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F23" s="169">
         <v>5</v>
@@ -28936,15 +28936,15 @@
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C24" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="D24" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F24" s="169">
         <v>6</v>
@@ -28974,15 +28974,15 @@
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D25" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="F25" s="169">
         <v>7</v>
@@ -29012,15 +29012,15 @@
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C26" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D26" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="F26" s="169">
         <v>8</v>
@@ -29050,15 +29050,15 @@
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="C27" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D27" s="168">
         <f t="shared" ca="1" si="2"/>
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F27" s="169">
         <v>9</v>
@@ -29112,29 +29112,29 @@
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="264" t="s">
+      <c r="B30" s="322" t="s">
         <v>873</v>
       </c>
-      <c r="C30" s="264"/>
-      <c r="D30" s="264"/>
-      <c r="F30" s="260" t="s">
+      <c r="C30" s="322"/>
+      <c r="D30" s="322"/>
+      <c r="F30" s="318" t="s">
         <v>904</v>
       </c>
-      <c r="G30" s="260"/>
-      <c r="H30" s="260"/>
+      <c r="G30" s="318"/>
+      <c r="H30" s="318"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="209" cm="1">
         <f t="array" aca="1" ref="B31:D40" ca="1">_xlfn.RANDARRAY(10,3,0,100,TRUE)</f>
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C31" s="168">
         <f ca="1"/>
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D31" s="168">
         <f ca="1"/>
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="F31" s="167" t="s">
         <v>901</v>
@@ -29145,26 +29145,26 @@
       <c r="H31" s="167" t="s">
         <v>904</v>
       </c>
-      <c r="J31" s="260" t="s">
+      <c r="J31" s="318" t="s">
         <v>912</v>
       </c>
-      <c r="K31" s="260"/>
-      <c r="L31" s="260"/>
-      <c r="M31" s="260"/>
-      <c r="N31" s="260"/>
+      <c r="K31" s="318"/>
+      <c r="L31" s="318"/>
+      <c r="M31" s="318"/>
+      <c r="N31" s="318"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="209">
         <f ca="1"/>
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="C32" s="168">
         <f ca="1"/>
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D32" s="168">
         <f ca="1"/>
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="F32" s="169">
         <v>1</v>
@@ -29188,22 +29188,22 @@
       <c r="M32" s="167" t="s">
         <v>907</v>
       </c>
-      <c r="N32" s="265" t="s">
+      <c r="N32" s="236" t="s">
         <v>858</v>
       </c>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="209">
         <f ca="1"/>
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C33" s="168">
         <f ca="1"/>
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D33" s="168">
         <f ca="1"/>
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F33" s="169">
         <v>2</v>
@@ -29237,15 +29237,15 @@
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B34" s="209">
         <f ca="1"/>
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C34" s="168">
         <f ca="1"/>
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="D34" s="168">
         <f ca="1"/>
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="F34" s="169">
         <v>3</v>
@@ -29279,15 +29279,15 @@
     <row r="35" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B35" s="209">
         <f ca="1"/>
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="C35" s="168">
         <f ca="1"/>
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="D35" s="168">
         <f ca="1"/>
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="F35" s="169">
         <v>4</v>
@@ -29321,15 +29321,15 @@
     <row r="36" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B36" s="209">
         <f ca="1"/>
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C36" s="168">
         <f ca="1"/>
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="D36" s="168">
         <f ca="1"/>
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F36" s="169">
         <v>5</v>
@@ -29363,15 +29363,15 @@
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B37" s="209">
         <f ca="1"/>
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C37" s="168">
         <f ca="1"/>
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D37" s="168">
         <f ca="1"/>
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="F37" s="169">
         <v>6</v>
@@ -29405,15 +29405,15 @@
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B38" s="209">
         <f ca="1"/>
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C38" s="168">
         <f ca="1"/>
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D38" s="168">
         <f ca="1"/>
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="F38" s="169">
         <v>7</v>
@@ -29447,15 +29447,15 @@
     <row r="39" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B39" s="209">
         <f ca="1"/>
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C39" s="168">
         <f ca="1"/>
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D39" s="168">
         <f ca="1"/>
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="F39" s="169">
         <v>8</v>
@@ -29489,15 +29489,15 @@
     <row r="40" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B40" s="209">
         <f ca="1"/>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C40" s="168">
         <f ca="1"/>
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="D40" s="168">
         <f ca="1"/>
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F40" s="169">
         <v>9</v>
@@ -29579,16 +29579,16 @@
       </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B43" s="260" t="s">
+      <c r="B43" s="318" t="s">
         <v>813</v>
       </c>
-      <c r="C43" s="260"/>
-      <c r="D43" s="260"/>
-      <c r="F43" s="260" t="s">
+      <c r="C43" s="318"/>
+      <c r="D43" s="318"/>
+      <c r="F43" s="318" t="s">
         <v>818</v>
       </c>
-      <c r="G43" s="260"/>
-      <c r="H43" s="260"/>
+      <c r="G43" s="318"/>
+      <c r="H43" s="318"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B44" s="167" t="s">
@@ -29630,15 +29630,15 @@
         <f t="array" ref="H45:H54">SMALL($G$45:$G$54,F45:F54)</f>
         <v>128</v>
       </c>
-      <c r="J45" s="260" t="s">
+      <c r="J45" s="318" t="s">
         <v>913</v>
       </c>
-      <c r="K45" s="260"/>
-      <c r="L45" s="260"/>
-      <c r="M45" s="260"/>
-      <c r="N45" s="260"/>
-      <c r="O45" s="260"/>
-      <c r="P45" s="260"/>
+      <c r="K45" s="318"/>
+      <c r="L45" s="318"/>
+      <c r="M45" s="318"/>
+      <c r="N45" s="318"/>
+      <c r="O45" s="318"/>
+      <c r="P45" s="318"/>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B46" s="169">
@@ -29665,19 +29665,19 @@
       <c r="K46" s="167" t="s">
         <v>902</v>
       </c>
-      <c r="L46" s="267" t="s">
+      <c r="L46" s="237" t="s">
         <v>914</v>
       </c>
       <c r="M46" s="167" t="s">
         <v>878</v>
       </c>
-      <c r="N46" s="265" t="s">
+      <c r="N46" s="236" t="s">
         <v>883</v>
       </c>
-      <c r="O46" s="265" t="s">
+      <c r="O46" s="236" t="s">
         <v>888</v>
       </c>
-      <c r="P46" s="265" t="s">
+      <c r="P46" s="236" t="s">
         <v>893</v>
       </c>
     </row>
@@ -30144,597 +30144,597 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="269" t="s">
+      <c r="B3" s="239" t="s">
         <v>559</v>
       </c>
-      <c r="C3" s="269" t="s">
+      <c r="C3" s="239" t="s">
         <v>560</v>
       </c>
-      <c r="D3" s="269" t="s">
+      <c r="D3" s="239" t="s">
         <v>561</v>
       </c>
-      <c r="E3" s="269" t="s">
+      <c r="E3" s="239" t="s">
         <v>752</v>
       </c>
-      <c r="F3" s="269" t="s">
+      <c r="F3" s="239" t="s">
         <v>562</v>
       </c>
-      <c r="G3" s="269" t="s">
+      <c r="G3" s="239" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="270">
+      <c r="B4" s="240">
         <v>1</v>
       </c>
-      <c r="C4" s="271" t="s">
+      <c r="C4" s="241" t="s">
         <v>915</v>
       </c>
-      <c r="D4" s="272" t="s">
+      <c r="D4" s="242" t="s">
         <v>916</v>
       </c>
-      <c r="E4" s="272" t="s">
+      <c r="E4" s="242" t="s">
         <v>917</v>
       </c>
-      <c r="F4" s="272" t="s">
+      <c r="F4" s="242" t="s">
         <v>918</v>
       </c>
-      <c r="G4" s="272" t="s">
+      <c r="G4" s="242" t="s">
         <v>916</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="270">
+      <c r="B5" s="240">
         <v>2</v>
       </c>
-      <c r="C5" s="271" t="s">
+      <c r="C5" s="241" t="s">
         <v>919</v>
       </c>
-      <c r="D5" s="272" t="s">
+      <c r="D5" s="242" t="s">
         <v>920</v>
       </c>
-      <c r="E5" s="272" t="s">
+      <c r="E5" s="242" t="s">
         <v>921</v>
       </c>
-      <c r="F5" s="272" t="s">
+      <c r="F5" s="242" t="s">
         <v>922</v>
       </c>
-      <c r="G5" s="272" t="s">
+      <c r="G5" s="242" t="s">
         <v>920</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="282">
+      <c r="B6" s="249">
         <v>3</v>
       </c>
-      <c r="C6" s="283" t="s">
+      <c r="C6" s="250" t="s">
         <v>923</v>
       </c>
-      <c r="D6" s="284" t="s">
+      <c r="D6" s="251" t="s">
         <v>924</v>
       </c>
-      <c r="E6" s="284" t="s">
+      <c r="E6" s="251" t="s">
         <v>925</v>
       </c>
-      <c r="F6" s="284" t="s">
+      <c r="F6" s="251" t="s">
         <v>926</v>
       </c>
-      <c r="G6" s="284" t="s">
+      <c r="G6" s="251" t="s">
         <v>927</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="282">
+      <c r="B7" s="249">
         <v>4</v>
       </c>
-      <c r="C7" s="283" t="s">
+      <c r="C7" s="250" t="s">
         <v>928</v>
       </c>
-      <c r="D7" s="284" t="s">
+      <c r="D7" s="251" t="s">
         <v>929</v>
       </c>
-      <c r="E7" s="284" t="s">
+      <c r="E7" s="251" t="s">
         <v>930</v>
       </c>
-      <c r="F7" s="284" t="s">
+      <c r="F7" s="251" t="s">
         <v>931</v>
       </c>
-      <c r="G7" s="284" t="s">
+      <c r="G7" s="251" t="s">
         <v>932</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="282">
+      <c r="B8" s="249">
         <v>5</v>
       </c>
-      <c r="C8" s="283" t="s">
+      <c r="C8" s="250" t="s">
         <v>933</v>
       </c>
-      <c r="D8" s="284" t="s">
+      <c r="D8" s="251" t="s">
         <v>934</v>
       </c>
-      <c r="E8" s="284" t="s">
+      <c r="E8" s="251" t="s">
         <v>935</v>
       </c>
-      <c r="F8" s="284" t="s">
+      <c r="F8" s="251" t="s">
         <v>936</v>
       </c>
-      <c r="G8" s="284" t="s">
+      <c r="G8" s="251" t="s">
         <v>937</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="282">
+      <c r="B9" s="249">
         <v>6</v>
       </c>
-      <c r="C9" s="283" t="s">
+      <c r="C9" s="250" t="s">
         <v>938</v>
       </c>
-      <c r="D9" s="284" t="s">
+      <c r="D9" s="251" t="s">
         <v>939</v>
       </c>
-      <c r="E9" s="284" t="s">
+      <c r="E9" s="251" t="s">
         <v>940</v>
       </c>
-      <c r="F9" s="284" t="s">
+      <c r="F9" s="251" t="s">
         <v>941</v>
       </c>
-      <c r="G9" s="284" t="s">
+      <c r="G9" s="251" t="s">
         <v>942</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="282">
+      <c r="B10" s="249">
         <v>7</v>
       </c>
-      <c r="C10" s="283" t="s">
+      <c r="C10" s="250" t="s">
         <v>943</v>
       </c>
-      <c r="D10" s="284" t="s">
+      <c r="D10" s="251" t="s">
         <v>944</v>
       </c>
-      <c r="E10" s="284" t="s">
+      <c r="E10" s="251" t="s">
         <v>945</v>
       </c>
-      <c r="F10" s="284" t="s">
+      <c r="F10" s="251" t="s">
         <v>946</v>
       </c>
-      <c r="G10" s="284" t="s">
+      <c r="G10" s="251" t="s">
         <v>947</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="282">
+      <c r="B11" s="249">
         <v>8</v>
       </c>
-      <c r="C11" s="283" t="s">
+      <c r="C11" s="250" t="s">
         <v>948</v>
       </c>
-      <c r="D11" s="284" t="s">
+      <c r="D11" s="251" t="s">
         <v>949</v>
       </c>
-      <c r="E11" s="284" t="s">
+      <c r="E11" s="251" t="s">
         <v>950</v>
       </c>
-      <c r="F11" s="284" t="s">
+      <c r="F11" s="251" t="s">
         <v>951</v>
       </c>
-      <c r="G11" s="284" t="s">
+      <c r="G11" s="251" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="282">
+      <c r="B12" s="249">
         <v>9</v>
       </c>
-      <c r="C12" s="283" t="s">
+      <c r="C12" s="250" t="s">
         <v>953</v>
       </c>
-      <c r="D12" s="284" t="s">
+      <c r="D12" s="251" t="s">
         <v>954</v>
       </c>
-      <c r="E12" s="284" t="s">
+      <c r="E12" s="251" t="s">
         <v>955</v>
       </c>
-      <c r="F12" s="284" t="s">
+      <c r="F12" s="251" t="s">
         <v>951</v>
       </c>
-      <c r="G12" s="284" t="s">
+      <c r="G12" s="251" t="s">
         <v>956</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="282">
+      <c r="B13" s="249">
         <v>10</v>
       </c>
-      <c r="C13" s="283" t="s">
+      <c r="C13" s="250" t="s">
         <v>957</v>
       </c>
-      <c r="D13" s="284" t="s">
+      <c r="D13" s="251" t="s">
         <v>958</v>
       </c>
-      <c r="E13" s="284" t="s">
+      <c r="E13" s="251" t="s">
         <v>959</v>
       </c>
-      <c r="F13" s="284" t="s">
+      <c r="F13" s="251" t="s">
         <v>951</v>
       </c>
-      <c r="G13" s="284" t="s">
+      <c r="G13" s="251" t="s">
         <v>960</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="300">
+      <c r="B14" s="267">
         <v>11</v>
       </c>
-      <c r="C14" s="301" t="s">
+      <c r="C14" s="268" t="s">
         <v>961</v>
       </c>
-      <c r="D14" s="302" t="s">
+      <c r="D14" s="269" t="s">
         <v>962</v>
       </c>
-      <c r="E14" s="302" t="s">
+      <c r="E14" s="269" t="s">
         <v>963</v>
       </c>
-      <c r="F14" s="302" t="s">
+      <c r="F14" s="269" t="s">
         <v>964</v>
       </c>
-      <c r="G14" s="302" t="s">
+      <c r="G14" s="269" t="s">
         <v>965</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="300">
+      <c r="B15" s="267">
         <v>12</v>
       </c>
-      <c r="C15" s="301" t="s">
+      <c r="C15" s="268" t="s">
         <v>966</v>
       </c>
-      <c r="D15" s="302" t="s">
+      <c r="D15" s="269" t="s">
         <v>967</v>
       </c>
-      <c r="E15" s="302" t="s">
+      <c r="E15" s="269" t="s">
         <v>968</v>
       </c>
-      <c r="F15" s="302" t="s">
+      <c r="F15" s="269" t="s">
         <v>969</v>
       </c>
-      <c r="G15" s="302" t="s">
+      <c r="G15" s="269" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="300">
+      <c r="B16" s="267">
         <v>13</v>
       </c>
-      <c r="C16" s="301" t="s">
+      <c r="C16" s="268" t="s">
         <v>971</v>
       </c>
-      <c r="D16" s="302" t="s">
+      <c r="D16" s="269" t="s">
         <v>972</v>
       </c>
-      <c r="E16" s="302" t="s">
+      <c r="E16" s="269" t="s">
         <v>973</v>
       </c>
-      <c r="F16" s="302" t="s">
+      <c r="F16" s="269" t="s">
         <v>974</v>
       </c>
-      <c r="G16" s="302" t="s">
+      <c r="G16" s="269" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="297">
+      <c r="B17" s="264">
         <v>14</v>
       </c>
-      <c r="C17" s="298" t="s">
+      <c r="C17" s="265" t="s">
         <v>976</v>
       </c>
-      <c r="D17" s="299" t="s">
+      <c r="D17" s="266" t="s">
         <v>977</v>
       </c>
-      <c r="E17" s="299" t="s">
+      <c r="E17" s="266" t="s">
         <v>978</v>
       </c>
-      <c r="F17" s="299" t="s">
+      <c r="F17" s="266" t="s">
         <v>979</v>
       </c>
-      <c r="G17" s="299" t="s">
+      <c r="G17" s="266" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="297">
+      <c r="B18" s="264">
         <v>15</v>
       </c>
-      <c r="C18" s="298" t="s">
+      <c r="C18" s="265" t="s">
         <v>981</v>
       </c>
-      <c r="D18" s="299" t="s">
+      <c r="D18" s="266" t="s">
         <v>982</v>
       </c>
-      <c r="E18" s="299" t="s">
+      <c r="E18" s="266" t="s">
         <v>983</v>
       </c>
-      <c r="F18" s="299" t="s">
+      <c r="F18" s="266" t="s">
         <v>984</v>
       </c>
-      <c r="G18" s="299" t="s">
+      <c r="G18" s="266" t="s">
         <v>985</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="312">
+      <c r="B19" s="279">
         <v>16</v>
       </c>
-      <c r="C19" s="313" t="s">
+      <c r="C19" s="280" t="s">
         <v>986</v>
       </c>
-      <c r="D19" s="314" t="s">
+      <c r="D19" s="281" t="s">
         <v>987</v>
       </c>
-      <c r="E19" s="314" t="s">
+      <c r="E19" s="281" t="s">
         <v>988</v>
       </c>
-      <c r="F19" s="314" t="s">
+      <c r="F19" s="281" t="s">
         <v>989</v>
       </c>
-      <c r="G19" s="314" t="s">
+      <c r="G19" s="281" t="s">
         <v>990</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="273">
+      <c r="B20" s="243">
         <v>17</v>
       </c>
-      <c r="C20" s="274" t="s">
+      <c r="C20" s="244" t="s">
         <v>991</v>
       </c>
-      <c r="D20" s="275" t="s">
+      <c r="D20" s="245" t="s">
         <v>992</v>
       </c>
-      <c r="E20" s="275" t="s">
+      <c r="E20" s="245" t="s">
         <v>993</v>
       </c>
-      <c r="F20" s="275" t="s">
+      <c r="F20" s="245" t="s">
         <v>994</v>
       </c>
-      <c r="G20" s="275" t="s">
+      <c r="G20" s="245" t="s">
         <v>995</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="273">
+      <c r="B21" s="243">
         <v>18</v>
       </c>
-      <c r="C21" s="274" t="s">
+      <c r="C21" s="244" t="s">
         <v>996</v>
       </c>
-      <c r="D21" s="275" t="s">
+      <c r="D21" s="245" t="s">
         <v>997</v>
       </c>
-      <c r="E21" s="275" t="s">
+      <c r="E21" s="245" t="s">
         <v>998</v>
       </c>
-      <c r="F21" s="275" t="s">
+      <c r="F21" s="245" t="s">
         <v>134</v>
       </c>
-      <c r="G21" s="275" t="s">
+      <c r="G21" s="245" t="s">
         <v>999</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="291">
+      <c r="B22" s="258">
         <v>19</v>
       </c>
-      <c r="C22" s="292" t="s">
+      <c r="C22" s="259" t="s">
         <v>1000</v>
       </c>
-      <c r="D22" s="293" t="s">
+      <c r="D22" s="260" t="s">
         <v>1001</v>
       </c>
-      <c r="E22" s="293" t="s">
+      <c r="E22" s="260" t="s">
         <v>1002</v>
       </c>
-      <c r="F22" s="293" t="s">
+      <c r="F22" s="260" t="s">
         <v>1003</v>
       </c>
-      <c r="G22" s="293" t="s">
+      <c r="G22" s="260" t="s">
         <v>1004</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="291">
+      <c r="B23" s="258">
         <v>20</v>
       </c>
-      <c r="C23" s="292" t="s">
+      <c r="C23" s="259" t="s">
         <v>1005</v>
       </c>
-      <c r="D23" s="293" t="s">
+      <c r="D23" s="260" t="s">
         <v>1006</v>
       </c>
-      <c r="E23" s="293" t="s">
+      <c r="E23" s="260" t="s">
         <v>1007</v>
       </c>
-      <c r="F23" s="293" t="s">
+      <c r="F23" s="260" t="s">
         <v>1008</v>
       </c>
-      <c r="G23" s="293" t="s">
+      <c r="G23" s="260" t="s">
         <v>1009</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="294">
+      <c r="B24" s="261">
         <v>21</v>
       </c>
-      <c r="C24" s="295" t="s">
+      <c r="C24" s="262" t="s">
         <v>1010</v>
       </c>
-      <c r="D24" s="296" t="s">
+      <c r="D24" s="263" t="s">
         <v>1011</v>
       </c>
-      <c r="E24" s="296" t="s">
+      <c r="E24" s="263" t="s">
         <v>1012</v>
       </c>
-      <c r="F24" s="296" t="s">
+      <c r="F24" s="263" t="s">
         <v>1013</v>
       </c>
-      <c r="G24" s="296" t="s">
+      <c r="G24" s="263" t="s">
         <v>1014</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="294">
+      <c r="B25" s="261">
         <v>22</v>
       </c>
-      <c r="C25" s="295" t="s">
+      <c r="C25" s="262" t="s">
         <v>1015</v>
       </c>
-      <c r="D25" s="296" t="s">
+      <c r="D25" s="263" t="s">
         <v>1016</v>
       </c>
-      <c r="E25" s="296" t="s">
+      <c r="E25" s="263" t="s">
         <v>1017</v>
       </c>
-      <c r="F25" s="296" t="s">
+      <c r="F25" s="263" t="s">
         <v>1018</v>
       </c>
-      <c r="G25" s="296" t="s">
+      <c r="G25" s="263" t="s">
         <v>1019</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="312">
+      <c r="B26" s="279">
         <v>23</v>
       </c>
-      <c r="C26" s="313" t="s">
+      <c r="C26" s="280" t="s">
         <v>1020</v>
       </c>
-      <c r="D26" s="314" t="s">
+      <c r="D26" s="281" t="s">
         <v>1021</v>
       </c>
-      <c r="E26" s="314" t="s">
+      <c r="E26" s="281" t="s">
         <v>1022</v>
       </c>
-      <c r="F26" s="314" t="s">
+      <c r="F26" s="281" t="s">
         <v>1023</v>
       </c>
-      <c r="G26" s="314" t="s">
+      <c r="G26" s="281" t="s">
         <v>1024</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="318">
+      <c r="B27" s="285">
         <v>24</v>
       </c>
-      <c r="C27" s="319" t="s">
+      <c r="C27" s="286" t="s">
         <v>628</v>
       </c>
-      <c r="D27" s="320" t="s">
+      <c r="D27" s="287" t="s">
         <v>1025</v>
       </c>
-      <c r="E27" s="320" t="s">
+      <c r="E27" s="287" t="s">
         <v>1026</v>
       </c>
-      <c r="F27" s="320" t="s">
+      <c r="F27" s="287" t="s">
         <v>1027</v>
       </c>
-      <c r="G27" s="320" t="s">
+      <c r="G27" s="287" t="s">
         <v>1028</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="321">
+      <c r="B28" s="288">
         <v>25</v>
       </c>
-      <c r="C28" s="322" t="s">
+      <c r="C28" s="289" t="s">
         <v>1029</v>
       </c>
-      <c r="D28" s="323" t="s">
+      <c r="D28" s="290" t="s">
         <v>1030</v>
       </c>
-      <c r="E28" s="323" t="s">
+      <c r="E28" s="290" t="s">
         <v>1031</v>
       </c>
-      <c r="F28" s="323" t="s">
+      <c r="F28" s="290" t="s">
         <v>1032</v>
       </c>
-      <c r="G28" s="323" t="s">
+      <c r="G28" s="290" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="321">
+      <c r="B29" s="288">
         <v>26</v>
       </c>
-      <c r="C29" s="322" t="s">
+      <c r="C29" s="289" t="s">
         <v>1034</v>
       </c>
-      <c r="D29" s="323" t="s">
+      <c r="D29" s="290" t="s">
         <v>1035</v>
       </c>
-      <c r="E29" s="323" t="s">
+      <c r="E29" s="290" t="s">
         <v>1036</v>
       </c>
-      <c r="F29" s="323" t="s">
+      <c r="F29" s="290" t="s">
         <v>1037</v>
       </c>
-      <c r="G29" s="323" t="s">
+      <c r="G29" s="290" t="s">
         <v>1038</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="315">
+      <c r="B30" s="282">
         <v>27</v>
       </c>
-      <c r="C30" s="316" t="s">
+      <c r="C30" s="283" t="s">
         <v>1039</v>
       </c>
-      <c r="D30" s="317" t="s">
+      <c r="D30" s="284" t="s">
         <v>1039</v>
       </c>
-      <c r="E30" s="317" t="s">
+      <c r="E30" s="284" t="s">
         <v>1040</v>
       </c>
-      <c r="F30" s="317" t="s">
+      <c r="F30" s="284" t="s">
         <v>1041</v>
       </c>
-      <c r="G30" s="317" t="s">
+      <c r="G30" s="284" t="s">
         <v>1042</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="315">
+      <c r="B31" s="282">
         <v>28</v>
       </c>
-      <c r="C31" s="316" t="s">
+      <c r="C31" s="283" t="s">
         <v>1043</v>
       </c>
-      <c r="D31" s="317" t="s">
+      <c r="D31" s="284" t="s">
         <v>1043</v>
       </c>
-      <c r="E31" s="317" t="s">
+      <c r="E31" s="284" t="s">
         <v>1044</v>
       </c>
-      <c r="F31" s="317" t="s">
+      <c r="F31" s="284" t="s">
         <v>1045</v>
       </c>
-      <c r="G31" s="317" t="s">
+      <c r="G31" s="284" t="s">
         <v>1046</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="276" t="s">
+      <c r="B32" s="324" t="s">
         <v>1047</v>
       </c>
-      <c r="C32" s="277"/>
-      <c r="D32" s="277"/>
-      <c r="E32" s="277"/>
-      <c r="F32" s="277"/>
-      <c r="G32" s="278"/>
+      <c r="C32" s="325"/>
+      <c r="D32" s="325"/>
+      <c r="E32" s="325"/>
+      <c r="F32" s="325"/>
+      <c r="G32" s="326"/>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="279"/>
+      <c r="B38" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -30761,48 +30761,48 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="280" t="s">
+      <c r="B3" s="247" t="s">
         <v>1055</v>
       </c>
-      <c r="C3" s="280" t="s">
+      <c r="C3" s="247" t="s">
         <v>1056</v>
       </c>
-      <c r="D3" s="280" t="s">
+      <c r="D3" s="247" t="s">
         <v>1057</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="281" t="s">
+      <c r="B4" s="248" t="s">
         <v>1053</v>
       </c>
-      <c r="C4" s="305">
+      <c r="C4" s="272">
         <v>46313</v>
       </c>
-      <c r="D4" s="306" t="str">
+      <c r="D4" s="273" t="str">
         <f ca="1">TEXT(TODAY(), "mm-dd-yyyy")</f>
-        <v>10-18-2026</v>
+        <v>10-19-2026</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="281" t="s">
+      <c r="B5" s="248" t="s">
         <v>1054</v>
       </c>
-      <c r="C5" s="307">
+      <c r="C5" s="274">
         <v>0.68472222222222223</v>
       </c>
-      <c r="D5" s="306" t="str">
+      <c r="D5" s="273" t="str">
         <f ca="1">TEXT(NOW()+7, "h:mm:ss AM/PM")</f>
-        <v>11:39:54 PM</v>
+        <v>10:45:18 AM</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="281" t="s">
+      <c r="B6" s="248" t="s">
         <v>1054</v>
       </c>
-      <c r="C6" s="307"/>
-      <c r="D6" s="306" t="str">
+      <c r="C6" s="274"/>
+      <c r="D6" s="273" t="str">
         <f ca="1">TEXT(NOW() + (7/24), "h:mm:ss AM/PM")</f>
-        <v>6:39:54 AM</v>
+        <v>5:45:18 PM</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -30827,452 +30827,452 @@
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="285">
+      <c r="B10" s="252">
         <v>46313</v>
       </c>
-      <c r="C10" s="308" t="str">
-        <f>TEXT(B10,"DDD")</f>
+      <c r="C10" s="275" t="str">
+        <f t="shared" ref="C10:C27" si="0">TEXT(B10,"DDD")</f>
         <v>Sun</v>
       </c>
-      <c r="D10" s="308">
+      <c r="D10" s="275">
         <f>DAY(B10)</f>
         <v>18</v>
       </c>
-      <c r="E10" s="308">
+      <c r="E10" s="275">
         <f>MONTH(B10)</f>
         <v>10</v>
       </c>
-      <c r="F10" s="308">
+      <c r="F10" s="275">
         <f>YEAR(B10)</f>
         <v>2026</v>
       </c>
-      <c r="G10" s="309">
+      <c r="G10" s="276">
         <f>DATE(F10,E10,D10)</f>
         <v>46313</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="285">
+      <c r="B11" s="252">
         <v>46314</v>
       </c>
-      <c r="C11" s="308" t="str">
-        <f>TEXT(B11,"DDD")</f>
+      <c r="C11" s="275" t="str">
+        <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="D11" s="308">
-        <f t="shared" ref="D11:D27" si="0">DAY(B11)</f>
+      <c r="D11" s="275">
+        <f t="shared" ref="D11:D27" si="1">DAY(B11)</f>
         <v>19</v>
       </c>
-      <c r="E11" s="308">
-        <f t="shared" ref="E11:E27" si="1">MONTH(B11)</f>
+      <c r="E11" s="275">
+        <f t="shared" ref="E11:E27" si="2">MONTH(B11)</f>
         <v>10</v>
       </c>
-      <c r="F11" s="308">
-        <f t="shared" ref="F11:F27" si="2">YEAR(B11)</f>
+      <c r="F11" s="275">
+        <f t="shared" ref="F11:F27" si="3">YEAR(B11)</f>
         <v>2026</v>
       </c>
-      <c r="G11" s="309">
-        <f t="shared" ref="G11:G27" si="3">DATE(F11,E11,D11)</f>
+      <c r="G11" s="276">
+        <f t="shared" ref="G11:G27" si="4">DATE(F11,E11,D11)</f>
         <v>46314</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="285">
+      <c r="B12" s="252">
         <v>46315</v>
       </c>
-      <c r="C12" s="308" t="str">
-        <f>TEXT(B12,"DDD")</f>
+      <c r="C12" s="275" t="str">
+        <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="D12" s="308">
+      <c r="D12" s="275">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="E12" s="275">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F12" s="275">
+        <f t="shared" si="3"/>
+        <v>2026</v>
+      </c>
+      <c r="G12" s="276">
+        <f t="shared" si="4"/>
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="252">
+        <v>46316</v>
+      </c>
+      <c r="C13" s="275" t="str">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="E12" s="308">
+        <v>Wed</v>
+      </c>
+      <c r="D13" s="275">
         <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="E13" s="275">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="F12" s="308">
+      <c r="F13" s="275">
+        <f t="shared" si="3"/>
+        <v>2026</v>
+      </c>
+      <c r="G13" s="276">
+        <f t="shared" si="4"/>
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="252">
+        <v>46317</v>
+      </c>
+      <c r="C14" s="275" t="str">
+        <f t="shared" si="0"/>
+        <v>Thu</v>
+      </c>
+      <c r="D14" s="275">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="E14" s="275">
         <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F14" s="275">
+        <f t="shared" si="3"/>
         <v>2026</v>
       </c>
-      <c r="G12" s="309">
+      <c r="G14" s="276">
+        <f t="shared" si="4"/>
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="252">
+        <v>46318</v>
+      </c>
+      <c r="C15" s="275" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="D15" s="275">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="E15" s="275">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F15" s="275">
         <f t="shared" si="3"/>
-        <v>46315</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="285">
-        <v>46316</v>
-      </c>
-      <c r="C13" s="308" t="str">
-        <f>TEXT(B13,"DDD")</f>
+        <v>2026</v>
+      </c>
+      <c r="G15" s="276">
+        <f t="shared" si="4"/>
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="252">
+        <v>46319</v>
+      </c>
+      <c r="C16" s="275" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="D16" s="275">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="E16" s="275">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F16" s="275">
+        <f t="shared" si="3"/>
+        <v>2026</v>
+      </c>
+      <c r="G16" s="276">
+        <f t="shared" si="4"/>
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="252">
+        <v>46320</v>
+      </c>
+      <c r="C17" s="275" t="str">
+        <f t="shared" si="0"/>
+        <v>Sun</v>
+      </c>
+      <c r="D17" s="275">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="E17" s="275">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F17" s="275">
+        <f t="shared" si="3"/>
+        <v>2026</v>
+      </c>
+      <c r="G17" s="276">
+        <f t="shared" si="4"/>
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="252">
+        <v>46321</v>
+      </c>
+      <c r="C18" s="275" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="D18" s="275">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="E18" s="275">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F18" s="275">
+        <f t="shared" si="3"/>
+        <v>2026</v>
+      </c>
+      <c r="G18" s="276">
+        <f t="shared" si="4"/>
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="252">
+        <v>46322</v>
+      </c>
+      <c r="C19" s="275" t="str">
+        <f t="shared" si="0"/>
+        <v>Tue</v>
+      </c>
+      <c r="D19" s="275">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="E19" s="275">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F19" s="275">
+        <f t="shared" si="3"/>
+        <v>2026</v>
+      </c>
+      <c r="G19" s="276">
+        <f t="shared" si="4"/>
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="252">
+        <v>46323</v>
+      </c>
+      <c r="C20" s="275" t="str">
+        <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="D13" s="308">
+      <c r="D20" s="275">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="E20" s="275">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F20" s="275">
+        <f t="shared" si="3"/>
+        <v>2026</v>
+      </c>
+      <c r="G20" s="276">
+        <f t="shared" si="4"/>
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="252">
+        <v>46324</v>
+      </c>
+      <c r="C21" s="275" t="str">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="E13" s="308">
+        <v>Thu</v>
+      </c>
+      <c r="D21" s="275">
         <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="E21" s="275">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="F13" s="308">
+      <c r="F21" s="275">
+        <f t="shared" si="3"/>
+        <v>2026</v>
+      </c>
+      <c r="G21" s="276">
+        <f t="shared" si="4"/>
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="252">
+        <v>46325</v>
+      </c>
+      <c r="C22" s="275" t="str">
+        <f t="shared" si="0"/>
+        <v>Fri</v>
+      </c>
+      <c r="D22" s="275">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="E22" s="275">
         <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F22" s="275">
+        <f t="shared" si="3"/>
         <v>2026</v>
       </c>
-      <c r="G13" s="309">
+      <c r="G22" s="276">
+        <f t="shared" si="4"/>
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="252">
+        <v>46326</v>
+      </c>
+      <c r="C23" s="275" t="str">
+        <f t="shared" si="0"/>
+        <v>Sat</v>
+      </c>
+      <c r="D23" s="275">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="E23" s="275">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F23" s="275">
         <f t="shared" si="3"/>
-        <v>46316</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="285">
-        <v>46317</v>
-      </c>
-      <c r="C14" s="308" t="str">
-        <f>TEXT(B14,"DDD")</f>
-        <v>Thu</v>
-      </c>
-      <c r="D14" s="308">
+        <v>2026</v>
+      </c>
+      <c r="G23" s="276">
+        <f t="shared" si="4"/>
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="252">
+        <v>46327</v>
+      </c>
+      <c r="C24" s="275" t="str">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="E14" s="308">
+        <v>Sun</v>
+      </c>
+      <c r="D24" s="275">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F14" s="308">
+        <v>1</v>
+      </c>
+      <c r="E24" s="275">
         <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="F24" s="275">
+        <f t="shared" si="3"/>
         <v>2026</v>
       </c>
-      <c r="G14" s="309">
+      <c r="G24" s="276">
+        <f t="shared" si="4"/>
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="252">
+        <v>46328</v>
+      </c>
+      <c r="C25" s="275" t="str">
+        <f t="shared" si="0"/>
+        <v>Mon</v>
+      </c>
+      <c r="D25" s="275">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E25" s="275">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="F25" s="275">
         <f t="shared" si="3"/>
-        <v>46317</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="285">
-        <v>46318</v>
-      </c>
-      <c r="C15" s="308" t="str">
-        <f>TEXT(B15,"DDD")</f>
-        <v>Fri</v>
-      </c>
-      <c r="D15" s="308">
+        <v>2026</v>
+      </c>
+      <c r="G25" s="276">
+        <f t="shared" si="4"/>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="252">
+        <v>46329</v>
+      </c>
+      <c r="C26" s="275" t="str">
         <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="E15" s="308">
+        <v>Tue</v>
+      </c>
+      <c r="D26" s="275">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F15" s="308">
+        <v>3</v>
+      </c>
+      <c r="E26" s="275">
         <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="F26" s="275">
+        <f t="shared" si="3"/>
         <v>2026</v>
       </c>
-      <c r="G15" s="309">
+      <c r="G26" s="276">
+        <f t="shared" si="4"/>
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="253">
+        <v>46330</v>
+      </c>
+      <c r="C27" s="275" t="str">
+        <f t="shared" si="0"/>
+        <v>Wed</v>
+      </c>
+      <c r="D27" s="275">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E27" s="275">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="F27" s="275">
         <f t="shared" si="3"/>
-        <v>46318</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="285">
-        <v>46319</v>
-      </c>
-      <c r="C16" s="308" t="str">
-        <f>TEXT(B16,"DDD")</f>
-        <v>Sat</v>
-      </c>
-      <c r="D16" s="308">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="E16" s="308">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F16" s="308">
-        <f t="shared" si="2"/>
         <v>2026</v>
       </c>
-      <c r="G16" s="309">
-        <f t="shared" si="3"/>
-        <v>46319</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="285">
-        <v>46320</v>
-      </c>
-      <c r="C17" s="308" t="str">
-        <f>TEXT(B17,"DDD")</f>
-        <v>Sun</v>
-      </c>
-      <c r="D17" s="308">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="E17" s="308">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F17" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G17" s="309">
-        <f t="shared" si="3"/>
-        <v>46320</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="285">
-        <v>46321</v>
-      </c>
-      <c r="C18" s="308" t="str">
-        <f>TEXT(B18,"DDD")</f>
-        <v>Mon</v>
-      </c>
-      <c r="D18" s="308">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="E18" s="308">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F18" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G18" s="309">
-        <f t="shared" si="3"/>
-        <v>46321</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="285">
-        <v>46322</v>
-      </c>
-      <c r="C19" s="308" t="str">
-        <f>TEXT(B19,"DDD")</f>
-        <v>Tue</v>
-      </c>
-      <c r="D19" s="308">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="E19" s="308">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F19" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G19" s="309">
-        <f t="shared" si="3"/>
-        <v>46322</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="285">
-        <v>46323</v>
-      </c>
-      <c r="C20" s="308" t="str">
-        <f>TEXT(B20,"DDD")</f>
-        <v>Wed</v>
-      </c>
-      <c r="D20" s="308">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="E20" s="308">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F20" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G20" s="309">
-        <f t="shared" si="3"/>
-        <v>46323</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="285">
-        <v>46324</v>
-      </c>
-      <c r="C21" s="308" t="str">
-        <f>TEXT(B21,"DDD")</f>
-        <v>Thu</v>
-      </c>
-      <c r="D21" s="308">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="E21" s="308">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F21" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G21" s="309">
-        <f t="shared" si="3"/>
-        <v>46324</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="285">
-        <v>46325</v>
-      </c>
-      <c r="C22" s="308" t="str">
-        <f>TEXT(B22,"DDD")</f>
-        <v>Fri</v>
-      </c>
-      <c r="D22" s="308">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="E22" s="308">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F22" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G22" s="309">
-        <f t="shared" si="3"/>
-        <v>46325</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="285">
-        <v>46326</v>
-      </c>
-      <c r="C23" s="308" t="str">
-        <f>TEXT(B23,"DDD")</f>
-        <v>Sat</v>
-      </c>
-      <c r="D23" s="308">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="E23" s="308">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="F23" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G23" s="309">
-        <f t="shared" si="3"/>
-        <v>46326</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="285">
-        <v>46327</v>
-      </c>
-      <c r="C24" s="308" t="str">
-        <f>TEXT(B24,"DDD")</f>
-        <v>Sun</v>
-      </c>
-      <c r="D24" s="308">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E24" s="308">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="F24" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G24" s="309">
-        <f t="shared" si="3"/>
-        <v>46327</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="285">
-        <v>46328</v>
-      </c>
-      <c r="C25" s="308" t="str">
-        <f>TEXT(B25,"DDD")</f>
-        <v>Mon</v>
-      </c>
-      <c r="D25" s="308">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E25" s="308">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="F25" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G25" s="309">
-        <f t="shared" si="3"/>
-        <v>46328</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="285">
-        <v>46329</v>
-      </c>
-      <c r="C26" s="308" t="str">
-        <f>TEXT(B26,"DDD")</f>
-        <v>Tue</v>
-      </c>
-      <c r="D26" s="308">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E26" s="308">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="F26" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G26" s="309">
-        <f t="shared" si="3"/>
-        <v>46329</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="286">
-        <v>46330</v>
-      </c>
-      <c r="C27" s="308" t="str">
-        <f>TEXT(B27,"DDD")</f>
-        <v>Wed</v>
-      </c>
-      <c r="D27" s="308">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E27" s="308">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="F27" s="308">
-        <f t="shared" si="2"/>
-        <v>2026</v>
-      </c>
-      <c r="G27" s="309">
-        <f t="shared" si="3"/>
+      <c r="G27" s="276">
+        <f t="shared" si="4"/>
         <v>46330</v>
       </c>
     </row>
@@ -31298,471 +31298,471 @@
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="287" t="str">
+      <c r="B32" s="254" t="str">
         <f ca="1">TEXT(NOW(), "h:mm:ss AM/PM")</f>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C32" s="308">
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C32" s="275">
         <f ca="1">HOUR(B32)</f>
-        <v>23</v>
-      </c>
-      <c r="D32" s="308">
+        <v>10</v>
+      </c>
+      <c r="D32" s="275">
         <f ca="1">MINUTE(B32)</f>
-        <v>39</v>
-      </c>
-      <c r="E32" s="308">
+        <v>45</v>
+      </c>
+      <c r="E32" s="275">
         <f ca="1">SECOND(B32)</f>
-        <v>54</v>
-      </c>
-      <c r="F32" s="308" t="str">
-        <f>TEXT(A1,"AM/PM")</f>
+        <v>18</v>
+      </c>
+      <c r="F32" s="275" t="str">
+        <f t="shared" ref="F32:F49" si="5">TEXT(A1,"AM/PM")</f>
         <v>AM</v>
       </c>
-      <c r="G32" s="310">
-        <f ca="1">TIME(C32,D32,E32)</f>
-        <v>0.98604166666666671</v>
+      <c r="G32" s="277">
+        <f t="shared" ref="G32:G49" ca="1" si="6">TIME(C32,D32,E32)</f>
+        <v>0.448125</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="287" t="str">
-        <f t="shared" ref="B33:B49" ca="1" si="4">TEXT(NOW(), "h:mm:ss AM/PM")</f>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C33" s="308">
-        <f t="shared" ref="C33:C49" ca="1" si="5">HOUR(B33)</f>
-        <v>23</v>
-      </c>
-      <c r="D33" s="308">
-        <f t="shared" ref="D33:D49" ca="1" si="6">MINUTE(B33)</f>
-        <v>39</v>
-      </c>
-      <c r="E33" s="308">
-        <f t="shared" ref="E33:E49" ca="1" si="7">SECOND(B33)</f>
-        <v>54</v>
-      </c>
-      <c r="F33" s="308" t="str">
-        <f>TEXT(A2,"AM/PM")</f>
+      <c r="B33" s="254" t="str">
+        <f t="shared" ref="B33:B49" ca="1" si="7">TEXT(NOW(), "h:mm:ss AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C33" s="275">
+        <f t="shared" ref="C33:C49" ca="1" si="8">HOUR(B33)</f>
+        <v>10</v>
+      </c>
+      <c r="D33" s="275">
+        <f t="shared" ref="D33:D49" ca="1" si="9">MINUTE(B33)</f>
+        <v>45</v>
+      </c>
+      <c r="E33" s="275">
+        <f t="shared" ref="E33:E49" ca="1" si="10">SECOND(B33)</f>
+        <v>18</v>
+      </c>
+      <c r="F33" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G33" s="310">
-        <f ca="1">TIME(C33,D33,E33)</f>
-        <v>0.98604166666666671</v>
+      <c r="G33" s="277">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.448125</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C34" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D34" s="308">
+      <c r="B34" s="254" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C34" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D34" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E34" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F34" s="275" t="str">
+        <f t="shared" si="5"/>
+        <v>AM</v>
+      </c>
+      <c r="G34" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E34" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F34" s="308" t="str">
-        <f>TEXT(A3,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C35" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D35" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E35" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F35" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G34" s="310">
-        <f ca="1">TIME(C34,D34,E34)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C35" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D35" s="308">
+      <c r="G35" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E35" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F35" s="308" t="str">
-        <f>TEXT(A4,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C36" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D36" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E36" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F36" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G35" s="310">
-        <f ca="1">TIME(C35,D35,E35)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B36" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C36" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D36" s="308">
+      <c r="G36" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E36" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F36" s="308" t="str">
-        <f>TEXT(A5,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C37" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D37" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E37" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F37" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G36" s="310">
-        <f ca="1">TIME(C36,D36,E36)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C37" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D37" s="308">
+      <c r="G37" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E37" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F37" s="308" t="str">
-        <f>TEXT(A6,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C38" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D38" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E38" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F38" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G37" s="310">
-        <f ca="1">TIME(C37,D37,E37)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C38" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D38" s="308">
+      <c r="G38" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E38" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F38" s="308" t="str">
-        <f>TEXT(A7,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C39" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D39" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E39" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F39" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G38" s="310">
-        <f ca="1">TIME(C38,D38,E38)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C39" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D39" s="308">
+      <c r="G39" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E39" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F39" s="308" t="str">
-        <f>TEXT(A8,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C40" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D40" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E40" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F40" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G39" s="310">
-        <f ca="1">TIME(C39,D39,E39)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C40" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D40" s="308">
+      <c r="G40" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E40" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F40" s="308" t="str">
-        <f>TEXT(A9,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C41" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D41" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E41" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F41" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G40" s="310">
-        <f ca="1">TIME(C40,D40,E40)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C41" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D41" s="308">
+      <c r="G41" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E41" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F41" s="308" t="str">
-        <f>TEXT(A10,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C42" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D42" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E42" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F42" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G41" s="310">
-        <f ca="1">TIME(C41,D41,E41)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C42" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D42" s="308">
+      <c r="G42" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E42" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F42" s="308" t="str">
-        <f>TEXT(A11,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C43" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D43" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E43" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F43" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G42" s="310">
-        <f ca="1">TIME(C42,D42,E42)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C43" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D43" s="308">
+      <c r="G43" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E43" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F43" s="308" t="str">
-        <f>TEXT(A12,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C44" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D44" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E44" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F44" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G43" s="310">
-        <f ca="1">TIME(C43,D43,E43)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C44" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D44" s="308">
+      <c r="G44" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E44" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F44" s="308" t="str">
-        <f>TEXT(A13,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C45" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D45" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E45" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F45" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G44" s="310">
-        <f ca="1">TIME(C44,D44,E44)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C45" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D45" s="308">
+      <c r="G45" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E45" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F45" s="308" t="str">
-        <f>TEXT(A14,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C46" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D46" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E46" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F46" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G45" s="310">
-        <f ca="1">TIME(C45,D45,E45)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C46" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D46" s="308">
+      <c r="G46" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E46" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F46" s="308" t="str">
-        <f>TEXT(A15,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C47" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D47" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E47" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F47" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G46" s="310">
-        <f ca="1">TIME(C46,D46,E46)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C47" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D47" s="308">
+      <c r="G47" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E47" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F47" s="308" t="str">
-        <f>TEXT(A16,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C48" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D48" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E48" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F48" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G47" s="310">
-        <f ca="1">TIME(C47,D47,E47)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C48" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D48" s="308">
+      <c r="G48" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E48" s="308">
+        <v>0.448125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B49" s="254" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F48" s="308" t="str">
-        <f>TEXT(A17,"AM/PM")</f>
+        <v>10:45:18 AM</v>
+      </c>
+      <c r="C49" s="275">
+        <f t="shared" ca="1" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="D49" s="275">
+        <f t="shared" ca="1" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="E49" s="275">
+        <f t="shared" ca="1" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="F49" s="275" t="str">
+        <f t="shared" si="5"/>
         <v>AM</v>
       </c>
-      <c r="G48" s="310">
-        <f ca="1">TIME(C48,D48,E48)</f>
-        <v>0.98604166666666671</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B49" s="287" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>11:39:54 PM</v>
-      </c>
-      <c r="C49" s="308">
-        <f t="shared" ca="1" si="5"/>
-        <v>23</v>
-      </c>
-      <c r="D49" s="308">
+      <c r="G49" s="277">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
-      </c>
-      <c r="E49" s="308">
-        <f t="shared" ca="1" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="F49" s="308" t="str">
-        <f>TEXT(A18,"AM/PM")</f>
-        <v>AM</v>
-      </c>
-      <c r="G49" s="310">
-        <f ca="1">TIME(C49,D49,E49)</f>
-        <v>0.98604166666666671</v>
+        <v>0.448125</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -31796,600 +31796,600 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="288">
+      <c r="A54" s="255">
         <v>46335</v>
       </c>
-      <c r="B54" s="288">
+      <c r="B54" s="255">
         <v>46313</v>
       </c>
-      <c r="C54" s="289">
+      <c r="C54" s="256">
         <v>46331</v>
       </c>
-      <c r="D54" s="303">
+      <c r="D54" s="270">
         <f>_xlfn.DAYS(C54,B54)</f>
         <v>18</v>
       </c>
-      <c r="E54" s="303">
+      <c r="E54" s="270">
         <f>DAYS360(B54,C54,)</f>
         <v>17</v>
       </c>
-      <c r="F54" s="303">
-        <f>NETWORKDAYS(B54,C54)</f>
+      <c r="F54" s="270">
+        <f t="shared" ref="F54:F71" si="11">NETWORKDAYS(B54,C54)</f>
         <v>14</v>
       </c>
-      <c r="G54" s="303">
+      <c r="G54" s="270">
         <f>NETWORKDAYS(B54, C54, $A54:$A55)</f>
         <v>14</v>
       </c>
-      <c r="H54" s="303">
-        <f>NETWORKDAYS.INTL(B54, C54, "1010000")</f>
+      <c r="H54" s="270">
+        <f t="shared" ref="H54:H71" si="12">NETWORKDAYS.INTL(B54, C54, "1010000")</f>
         <v>13</v>
       </c>
-      <c r="I54" s="303">
-        <f>NETWORKDAYS.INTL(B54,C54,"1010000",$A$54:$A$55)</f>
+      <c r="I54" s="270">
+        <f t="shared" ref="I54:I71" si="13">NETWORKDAYS.INTL(B54,C54,"1010000",$A$54:$A$55)</f>
         <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="288">
+      <c r="A55" s="255">
         <v>46381</v>
       </c>
-      <c r="B55" s="288">
+      <c r="B55" s="255">
         <v>46314</v>
       </c>
-      <c r="C55" s="289">
+      <c r="C55" s="256">
         <v>46332</v>
       </c>
-      <c r="D55" s="303">
-        <f t="shared" ref="D55:D71" si="8">_xlfn.DAYS(C55,B55)</f>
+      <c r="D55" s="270">
+        <f t="shared" ref="D55:D71" si="14">_xlfn.DAYS(C55,B55)</f>
         <v>18</v>
       </c>
-      <c r="E55" s="303">
-        <f t="shared" ref="E55:E71" si="9">DAYS360(B55,C55,)</f>
+      <c r="E55" s="270">
+        <f t="shared" ref="E55:E71" si="15">DAYS360(B55,C55,)</f>
         <v>17</v>
       </c>
-      <c r="F55" s="303">
-        <f>NETWORKDAYS(B55,C55)</f>
+      <c r="F55" s="270">
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
-      <c r="G55" s="303">
-        <f>NETWORKDAYS(B55, C55, $A$54:$A$55)</f>
+      <c r="G55" s="270">
+        <f t="shared" ref="G55:G71" si="16">NETWORKDAYS(B55, C55, $A$54:$A$55)</f>
         <v>15</v>
       </c>
-      <c r="H55" s="303">
-        <f>NETWORKDAYS.INTL(B55, C55, "1010000")</f>
+      <c r="H55" s="270">
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="I55" s="303">
-        <f>NETWORKDAYS.INTL(B55,C55,"1010000",$A$54:$A$55)</f>
+      <c r="I55" s="270">
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="288"/>
-      <c r="B56" s="288">
+      <c r="A56" s="255"/>
+      <c r="B56" s="255">
         <v>46315</v>
       </c>
-      <c r="C56" s="289">
+      <c r="C56" s="256">
         <v>46333</v>
       </c>
-      <c r="D56" s="303">
-        <f t="shared" si="8"/>
+      <c r="D56" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E56" s="303">
-        <f t="shared" si="9"/>
+      <c r="E56" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F56" s="303">
-        <f>NETWORKDAYS(B56,C56)</f>
+      <c r="F56" s="270">
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
-      <c r="G56" s="303">
-        <f>NETWORKDAYS(B56, C56, $A$54:$A$55)</f>
+      <c r="G56" s="270">
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
-      <c r="H56" s="303">
-        <f>NETWORKDAYS.INTL(B56, C56, "1010000")</f>
+      <c r="H56" s="270">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="I56" s="303">
-        <f>NETWORKDAYS.INTL(B56,C56,"1010000",$A$54:$A$55)</f>
+      <c r="I56" s="270">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="288"/>
-      <c r="B57" s="288">
+      <c r="A57" s="255"/>
+      <c r="B57" s="255">
         <v>46316</v>
       </c>
-      <c r="C57" s="289">
+      <c r="C57" s="256">
         <v>46334</v>
       </c>
-      <c r="D57" s="303">
-        <f t="shared" si="8"/>
+      <c r="D57" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E57" s="303">
-        <f t="shared" si="9"/>
+      <c r="E57" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F57" s="303">
-        <f>NETWORKDAYS(B57,C57)</f>
+      <c r="F57" s="270">
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="G57" s="303">
-        <f>NETWORKDAYS(B57, C57, $A$54:$A$55)</f>
+      <c r="G57" s="270">
+        <f t="shared" si="16"/>
         <v>13</v>
       </c>
-      <c r="H57" s="303">
-        <f>NETWORKDAYS.INTL(B57, C57, "1010000")</f>
+      <c r="H57" s="270">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="I57" s="303">
-        <f>NETWORKDAYS.INTL(B57,C57,"1010000",$A$54:$A$55)</f>
+      <c r="I57" s="270">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="288"/>
-      <c r="B58" s="288">
+      <c r="A58" s="255"/>
+      <c r="B58" s="255">
         <v>46317</v>
       </c>
-      <c r="C58" s="289">
+      <c r="C58" s="256">
         <v>46335</v>
       </c>
-      <c r="D58" s="303">
-        <f t="shared" si="8"/>
+      <c r="D58" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E58" s="303">
-        <f t="shared" si="9"/>
+      <c r="E58" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F58" s="303">
-        <f>NETWORKDAYS(B58,C58)</f>
+      <c r="F58" s="270">
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="G58" s="303">
-        <f>NETWORKDAYS(B58, C58, $A$54:$A$55)</f>
+      <c r="G58" s="270">
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
-      <c r="H58" s="303">
-        <f>NETWORKDAYS.INTL(B58, C58, "1010000")</f>
+      <c r="H58" s="270">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="I58" s="303">
-        <f>NETWORKDAYS.INTL(B58,C58,"1010000",$A$54:$A$55)</f>
+      <c r="I58" s="270">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="288"/>
-      <c r="B59" s="288">
+      <c r="A59" s="255"/>
+      <c r="B59" s="255">
         <v>46318</v>
       </c>
-      <c r="C59" s="289">
+      <c r="C59" s="256">
         <v>46336</v>
       </c>
-      <c r="D59" s="303">
-        <f t="shared" si="8"/>
+      <c r="D59" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E59" s="303">
-        <f t="shared" si="9"/>
+      <c r="E59" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F59" s="303">
-        <f>NETWORKDAYS(B59,C59)</f>
+      <c r="F59" s="270">
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="G59" s="303">
-        <f>NETWORKDAYS(B59, C59, $A$54:$A$55)</f>
+      <c r="G59" s="270">
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
-      <c r="H59" s="303">
-        <f>NETWORKDAYS.INTL(B59, C59, "1010000")</f>
+      <c r="H59" s="270">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="I59" s="303">
-        <f>NETWORKDAYS.INTL(B59,C59,"1010000",$A$54:$A$55)</f>
+      <c r="I59" s="270">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="288"/>
-      <c r="B60" s="288">
+      <c r="A60" s="255"/>
+      <c r="B60" s="255">
         <v>46319</v>
       </c>
-      <c r="C60" s="289">
+      <c r="C60" s="256">
         <v>46337</v>
       </c>
-      <c r="D60" s="303">
-        <f t="shared" si="8"/>
+      <c r="D60" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E60" s="303">
-        <f t="shared" si="9"/>
+      <c r="E60" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F60" s="303">
-        <f>NETWORKDAYS(B60,C60)</f>
+      <c r="F60" s="270">
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="G60" s="303">
-        <f>NETWORKDAYS(B60, C60, $A$54:$A$55)</f>
+      <c r="G60" s="270">
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
-      <c r="H60" s="303">
-        <f>NETWORKDAYS.INTL(B60, C60, "1010000")</f>
+      <c r="H60" s="270">
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="I60" s="303">
-        <f>NETWORKDAYS.INTL(B60,C60,"1010000",$A$54:$A$55)</f>
+      <c r="I60" s="270">
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="288"/>
-      <c r="B61" s="288">
+      <c r="A61" s="255"/>
+      <c r="B61" s="255">
         <v>46320</v>
       </c>
-      <c r="C61" s="289">
+      <c r="C61" s="256">
         <v>46338</v>
       </c>
-      <c r="D61" s="303">
-        <f t="shared" si="8"/>
+      <c r="D61" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E61" s="303">
-        <f t="shared" si="9"/>
+      <c r="E61" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F61" s="303">
-        <f>NETWORKDAYS(B61,C61)</f>
+      <c r="F61" s="270">
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
-      <c r="G61" s="303">
-        <f>NETWORKDAYS(B61, C61, $A$54:$A$55)</f>
+      <c r="G61" s="270">
+        <f t="shared" si="16"/>
         <v>13</v>
       </c>
-      <c r="H61" s="303">
-        <f>NETWORKDAYS.INTL(B61, C61, "1010000")</f>
+      <c r="H61" s="270">
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="I61" s="303">
-        <f>NETWORKDAYS.INTL(B61,C61,"1010000",$A$54:$A$55)</f>
+      <c r="I61" s="270">
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="288"/>
-      <c r="B62" s="288">
+      <c r="A62" s="255"/>
+      <c r="B62" s="255">
         <v>46321</v>
       </c>
-      <c r="C62" s="289">
+      <c r="C62" s="256">
         <v>46339</v>
       </c>
-      <c r="D62" s="303">
-        <f t="shared" si="8"/>
+      <c r="D62" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E62" s="303">
-        <f t="shared" si="9"/>
+      <c r="E62" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F62" s="303">
-        <f>NETWORKDAYS(B62,C62)</f>
+      <c r="F62" s="270">
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
-      <c r="G62" s="303">
-        <f>NETWORKDAYS(B62, C62, $A$54:$A$55)</f>
+      <c r="G62" s="270">
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
-      <c r="H62" s="303">
-        <f>NETWORKDAYS.INTL(B62, C62, "1010000")</f>
+      <c r="H62" s="270">
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="I62" s="303">
-        <f>NETWORKDAYS.INTL(B62,C62,"1010000",$A$54:$A$55)</f>
+      <c r="I62" s="270">
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="288"/>
-      <c r="B63" s="288">
+      <c r="A63" s="255"/>
+      <c r="B63" s="255">
         <v>46322</v>
       </c>
-      <c r="C63" s="289">
+      <c r="C63" s="256">
         <v>46340</v>
       </c>
-      <c r="D63" s="303">
-        <f t="shared" si="8"/>
+      <c r="D63" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E63" s="303">
-        <f t="shared" si="9"/>
+      <c r="E63" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F63" s="303">
-        <f>NETWORKDAYS(B63,C63)</f>
+      <c r="F63" s="270">
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
-      <c r="G63" s="303">
-        <f>NETWORKDAYS(B63, C63, $A$54:$A$55)</f>
+      <c r="G63" s="270">
+        <f t="shared" si="16"/>
         <v>13</v>
       </c>
-      <c r="H63" s="303">
-        <f>NETWORKDAYS.INTL(B63, C63, "1010000")</f>
+      <c r="H63" s="270">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="I63" s="303">
-        <f>NETWORKDAYS.INTL(B63,C63,"1010000",$A$54:$A$55)</f>
+      <c r="I63" s="270">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="288"/>
-      <c r="B64" s="288">
+      <c r="A64" s="255"/>
+      <c r="B64" s="255">
         <v>46323</v>
       </c>
-      <c r="C64" s="289">
+      <c r="C64" s="256">
         <v>46341</v>
       </c>
-      <c r="D64" s="303">
-        <f t="shared" si="8"/>
+      <c r="D64" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E64" s="303">
-        <f t="shared" si="9"/>
+      <c r="E64" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F64" s="303">
-        <f>NETWORKDAYS(B64,C64)</f>
+      <c r="F64" s="270">
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="G64" s="303">
-        <f>NETWORKDAYS(B64, C64, $A$54:$A$55)</f>
+      <c r="G64" s="270">
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
-      <c r="H64" s="303">
-        <f>NETWORKDAYS.INTL(B64, C64, "1010000")</f>
+      <c r="H64" s="270">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="I64" s="303">
-        <f>NETWORKDAYS.INTL(B64,C64,"1010000",$A$54:$A$55)</f>
+      <c r="I64" s="270">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="288"/>
-      <c r="B65" s="288">
+      <c r="A65" s="255"/>
+      <c r="B65" s="255">
         <v>46324</v>
       </c>
-      <c r="C65" s="289">
+      <c r="C65" s="256">
         <v>46342</v>
       </c>
-      <c r="D65" s="303">
-        <f t="shared" si="8"/>
+      <c r="D65" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E65" s="303">
-        <f t="shared" si="9"/>
+      <c r="E65" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F65" s="303">
-        <f>NETWORKDAYS(B65,C65)</f>
+      <c r="F65" s="270">
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="G65" s="303">
-        <f>NETWORKDAYS(B65, C65, $A$54:$A$55)</f>
+      <c r="G65" s="270">
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
-      <c r="H65" s="303">
-        <f>NETWORKDAYS.INTL(B65, C65, "1010000")</f>
+      <c r="H65" s="270">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="I65" s="303">
-        <f>NETWORKDAYS.INTL(B65,C65,"1010000",$A$54:$A$55)</f>
+      <c r="I65" s="270">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="288"/>
-      <c r="B66" s="288">
+      <c r="A66" s="255"/>
+      <c r="B66" s="255">
         <v>46325</v>
       </c>
-      <c r="C66" s="289">
+      <c r="C66" s="256">
         <v>46343</v>
       </c>
-      <c r="D66" s="303">
-        <f t="shared" si="8"/>
+      <c r="D66" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E66" s="303">
-        <f t="shared" si="9"/>
+      <c r="E66" s="270">
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
-      <c r="F66" s="303">
-        <f>NETWORKDAYS(B66,C66)</f>
+      <c r="F66" s="270">
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="G66" s="303">
-        <f>NETWORKDAYS(B66, C66, $A$54:$A$55)</f>
+      <c r="G66" s="270">
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
-      <c r="H66" s="303">
-        <f>NETWORKDAYS.INTL(B66, C66, "1010000")</f>
+      <c r="H66" s="270">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="I66" s="303">
-        <f>NETWORKDAYS.INTL(B66,C66,"1010000",$A$54:$A$55)</f>
+      <c r="I66" s="270">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="288"/>
-      <c r="B67" s="288">
+      <c r="A67" s="255"/>
+      <c r="B67" s="255">
         <v>46326</v>
       </c>
-      <c r="C67" s="289">
+      <c r="C67" s="256">
         <v>46344</v>
       </c>
-      <c r="D67" s="303">
-        <f t="shared" si="8"/>
+      <c r="D67" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E67" s="303">
-        <f t="shared" si="9"/>
+      <c r="E67" s="270">
+        <f t="shared" si="15"/>
         <v>18</v>
       </c>
-      <c r="F67" s="303">
-        <f>NETWORKDAYS(B67,C67)</f>
+      <c r="F67" s="270">
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="G67" s="303">
-        <f>NETWORKDAYS(B67, C67, $A$54:$A$55)</f>
+      <c r="G67" s="270">
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
-      <c r="H67" s="303">
-        <f>NETWORKDAYS.INTL(B67, C67, "1010000")</f>
+      <c r="H67" s="270">
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="I67" s="303">
-        <f>NETWORKDAYS.INTL(B67,C67,"1010000",$A$54:$A$55)</f>
+      <c r="I67" s="270">
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="288"/>
-      <c r="B68" s="288">
+      <c r="A68" s="255"/>
+      <c r="B68" s="255">
         <v>46327</v>
       </c>
-      <c r="C68" s="289">
+      <c r="C68" s="256">
         <v>46345</v>
       </c>
-      <c r="D68" s="303">
-        <f t="shared" si="8"/>
+      <c r="D68" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E68" s="303">
-        <f t="shared" si="9"/>
+      <c r="E68" s="270">
+        <f t="shared" si="15"/>
         <v>18</v>
       </c>
-      <c r="F68" s="303">
-        <f>NETWORKDAYS(B68,C68)</f>
+      <c r="F68" s="270">
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
-      <c r="G68" s="303">
-        <f>NETWORKDAYS(B68, C68, $A$54:$A$55)</f>
+      <c r="G68" s="270">
+        <f t="shared" si="16"/>
         <v>13</v>
       </c>
-      <c r="H68" s="303">
-        <f>NETWORKDAYS.INTL(B68, C68, "1010000")</f>
+      <c r="H68" s="270">
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="I68" s="303">
-        <f>NETWORKDAYS.INTL(B68,C68,"1010000",$A$54:$A$55)</f>
+      <c r="I68" s="270">
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="288"/>
-      <c r="B69" s="288">
+      <c r="A69" s="255"/>
+      <c r="B69" s="255">
         <v>46328</v>
       </c>
-      <c r="C69" s="289">
+      <c r="C69" s="256">
         <v>46346</v>
       </c>
-      <c r="D69" s="303">
-        <f t="shared" si="8"/>
+      <c r="D69" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E69" s="303">
-        <f t="shared" si="9"/>
+      <c r="E69" s="270">
+        <f t="shared" si="15"/>
         <v>18</v>
       </c>
-      <c r="F69" s="303">
-        <f>NETWORKDAYS(B69,C69)</f>
+      <c r="F69" s="270">
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
-      <c r="G69" s="303">
-        <f>NETWORKDAYS(B69, C69, $A$54:$A$55)</f>
+      <c r="G69" s="270">
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
-      <c r="H69" s="303">
-        <f>NETWORKDAYS.INTL(B69, C69, "1010000")</f>
+      <c r="H69" s="270">
+        <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="I69" s="303">
-        <f>NETWORKDAYS.INTL(B69,C69,"1010000",$A$54:$A$55)</f>
+      <c r="I69" s="270">
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="288"/>
-      <c r="B70" s="288">
+      <c r="A70" s="255"/>
+      <c r="B70" s="255">
         <v>46329</v>
       </c>
-      <c r="C70" s="289">
+      <c r="C70" s="256">
         <v>46347</v>
       </c>
-      <c r="D70" s="303">
-        <f t="shared" si="8"/>
+      <c r="D70" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E70" s="303">
-        <f t="shared" si="9"/>
+      <c r="E70" s="270">
+        <f t="shared" si="15"/>
         <v>18</v>
       </c>
-      <c r="F70" s="303">
-        <f>NETWORKDAYS(B70,C70)</f>
+      <c r="F70" s="270">
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
-      <c r="G70" s="303">
-        <f>NETWORKDAYS(B70, C70, $A$54:$A$55)</f>
+      <c r="G70" s="270">
+        <f t="shared" si="16"/>
         <v>13</v>
       </c>
-      <c r="H70" s="303">
-        <f>NETWORKDAYS.INTL(B70, C70, "1010000")</f>
+      <c r="H70" s="270">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="I70" s="303">
-        <f>NETWORKDAYS.INTL(B70,C70,"1010000",$A$54:$A$55)</f>
+      <c r="I70" s="270">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="288"/>
-      <c r="B71" s="288">
+      <c r="A71" s="255"/>
+      <c r="B71" s="255">
         <v>46330</v>
       </c>
-      <c r="C71" s="289">
+      <c r="C71" s="256">
         <v>46348</v>
       </c>
-      <c r="D71" s="303">
-        <f t="shared" si="8"/>
+      <c r="D71" s="270">
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="E71" s="303">
-        <f t="shared" si="9"/>
+      <c r="E71" s="270">
+        <f t="shared" si="15"/>
         <v>18</v>
       </c>
-      <c r="F71" s="303">
-        <f>NETWORKDAYS(B71,C71)</f>
+      <c r="F71" s="270">
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="G71" s="303">
-        <f>NETWORKDAYS(B71, C71, $A$54:$A$55)</f>
+      <c r="G71" s="270">
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
-      <c r="H71" s="303">
-        <f>NETWORKDAYS.INTL(B71, C71, "1010000")</f>
+      <c r="H71" s="270">
+        <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="I71" s="303">
-        <f>NETWORKDAYS.INTL(B71,C71,"1010000",$A$54:$A$55)</f>
+      <c r="I71" s="270">
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
     </row>
@@ -32418,456 +32418,456 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="288">
+      <c r="A77" s="255">
         <v>46335</v>
       </c>
-      <c r="B77" s="288">
+      <c r="B77" s="255">
         <v>46313</v>
       </c>
-      <c r="C77" s="290">
+      <c r="C77" s="257">
         <v>5</v>
       </c>
-      <c r="D77" s="304">
+      <c r="D77" s="271">
         <f>WORKDAY(B77,C77)</f>
         <v>46318</v>
       </c>
-      <c r="E77" s="304">
+      <c r="E77" s="271">
         <f>WORKDAY(B77,C77,$A$77:$A$78)</f>
         <v>46318</v>
       </c>
-      <c r="F77" s="303">
+      <c r="F77" s="270">
         <f>WORKDAY.INTL(B77,C77,"1000001")</f>
         <v>46319</v>
       </c>
-      <c r="G77" s="303">
+      <c r="G77" s="270">
         <f>WORKDAY.INTL(B77,C77,2,A77:A78)</f>
         <v>46319</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="288">
+      <c r="A78" s="255">
         <v>46381</v>
       </c>
-      <c r="B78" s="288">
+      <c r="B78" s="255">
         <v>46314</v>
       </c>
-      <c r="C78" s="290">
+      <c r="C78" s="257">
         <v>19</v>
       </c>
-      <c r="D78" s="304">
-        <f t="shared" ref="D78:D94" si="10">WORKDAY(B78,C78)</f>
+      <c r="D78" s="271">
+        <f t="shared" ref="D78:D94" si="17">WORKDAY(B78,C78)</f>
         <v>46339</v>
       </c>
-      <c r="E78" s="304">
-        <f t="shared" ref="E78:E94" si="11">WORKDAY(B78,C78,$A$77:$A$78)</f>
+      <c r="E78" s="271">
+        <f t="shared" ref="E78:E94" si="18">WORKDAY(B78,C78,$A$77:$A$78)</f>
         <v>46342</v>
       </c>
-      <c r="F78" s="303">
-        <f t="shared" ref="F78:F94" si="12">WORKDAY.INTL(B78,C78,"1000001")</f>
+      <c r="F78" s="270">
+        <f t="shared" ref="F78:F94" si="19">WORKDAY.INTL(B78,C78,"1000001")</f>
         <v>46339</v>
       </c>
-      <c r="G78" s="303">
+      <c r="G78" s="270">
         <f>WORKDAY.INTL(B78,C78,2,A77:A79)</f>
         <v>46339</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="288"/>
-      <c r="B79" s="288">
+      <c r="A79" s="255"/>
+      <c r="B79" s="255">
         <v>46315</v>
       </c>
-      <c r="C79" s="290">
+      <c r="C79" s="257">
         <v>15</v>
       </c>
-      <c r="D79" s="304">
-        <f t="shared" si="10"/>
+      <c r="D79" s="271">
+        <f t="shared" si="17"/>
         <v>46336</v>
       </c>
-      <c r="E79" s="304">
-        <f t="shared" si="11"/>
+      <c r="E79" s="271">
+        <f t="shared" si="18"/>
         <v>46337</v>
       </c>
-      <c r="F79" s="303">
-        <f t="shared" si="12"/>
+      <c r="F79" s="270">
+        <f t="shared" si="19"/>
         <v>46336</v>
       </c>
-      <c r="G79" s="303">
+      <c r="G79" s="270">
         <f>WORKDAY.INTL(B79,C79,2,A79:A80)</f>
         <v>46336</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="288"/>
-      <c r="B80" s="288">
+      <c r="A80" s="255"/>
+      <c r="B80" s="255">
         <v>46316</v>
       </c>
-      <c r="C80" s="290">
+      <c r="C80" s="257">
         <v>18</v>
       </c>
-      <c r="D80" s="304">
-        <f t="shared" si="10"/>
+      <c r="D80" s="271">
+        <f t="shared" si="17"/>
         <v>46342</v>
       </c>
-      <c r="E80" s="304">
-        <f t="shared" si="11"/>
+      <c r="E80" s="271">
+        <f t="shared" si="18"/>
         <v>46343</v>
       </c>
-      <c r="F80" s="303">
-        <f t="shared" si="12"/>
+      <c r="F80" s="270">
+        <f t="shared" si="19"/>
         <v>46340</v>
       </c>
-      <c r="G80" s="303">
-        <f t="shared" ref="G80:G94" si="13">WORKDAY.INTL(B80,C80,2,A80:A81)</f>
+      <c r="G80" s="270">
+        <f t="shared" ref="G80:G94" si="20">WORKDAY.INTL(B80,C80,2,A80:A81)</f>
         <v>46340</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="288"/>
-      <c r="B81" s="288">
+      <c r="A81" s="255"/>
+      <c r="B81" s="255">
         <v>46317</v>
       </c>
-      <c r="C81" s="290">
+      <c r="C81" s="257">
         <v>19</v>
       </c>
-      <c r="D81" s="304">
-        <f t="shared" si="10"/>
+      <c r="D81" s="271">
+        <f t="shared" si="17"/>
         <v>46344</v>
       </c>
-      <c r="E81" s="304">
-        <f t="shared" si="11"/>
+      <c r="E81" s="271">
+        <f t="shared" si="18"/>
         <v>46345</v>
       </c>
-      <c r="F81" s="303">
-        <f t="shared" si="12"/>
+      <c r="F81" s="270">
+        <f t="shared" si="19"/>
         <v>46344</v>
       </c>
-      <c r="G81" s="303">
-        <f t="shared" si="13"/>
+      <c r="G81" s="270">
+        <f t="shared" si="20"/>
         <v>46344</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="288"/>
-      <c r="B82" s="288">
+      <c r="A82" s="255"/>
+      <c r="B82" s="255">
         <v>46318</v>
       </c>
-      <c r="C82" s="290">
+      <c r="C82" s="257">
         <v>8</v>
       </c>
-      <c r="D82" s="304">
-        <f t="shared" si="10"/>
+      <c r="D82" s="271">
+        <f t="shared" si="17"/>
         <v>46330</v>
       </c>
-      <c r="E82" s="304">
-        <f t="shared" si="11"/>
+      <c r="E82" s="271">
+        <f t="shared" si="18"/>
         <v>46330</v>
       </c>
-      <c r="F82" s="303">
-        <f t="shared" si="12"/>
+      <c r="F82" s="270">
+        <f t="shared" si="19"/>
         <v>46330</v>
       </c>
-      <c r="G82" s="303">
-        <f t="shared" si="13"/>
+      <c r="G82" s="270">
+        <f t="shared" si="20"/>
         <v>46330</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="288"/>
-      <c r="B83" s="288">
+      <c r="A83" s="255"/>
+      <c r="B83" s="255">
         <v>46319</v>
       </c>
-      <c r="C83" s="290">
+      <c r="C83" s="257">
         <v>8</v>
       </c>
-      <c r="D83" s="304">
-        <f t="shared" si="10"/>
+      <c r="D83" s="271">
+        <f t="shared" si="17"/>
         <v>46330</v>
       </c>
-      <c r="E83" s="304">
-        <f t="shared" si="11"/>
+      <c r="E83" s="271">
+        <f t="shared" si="18"/>
         <v>46330</v>
       </c>
-      <c r="F83" s="303">
-        <f t="shared" si="12"/>
+      <c r="F83" s="270">
+        <f t="shared" si="19"/>
         <v>46331</v>
       </c>
-      <c r="G83" s="303">
-        <f t="shared" si="13"/>
+      <c r="G83" s="270">
+        <f t="shared" si="20"/>
         <v>46331</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="288"/>
-      <c r="B84" s="288">
+      <c r="A84" s="255"/>
+      <c r="B84" s="255">
         <v>46320</v>
       </c>
-      <c r="C84" s="290">
+      <c r="C84" s="257">
         <v>19</v>
       </c>
-      <c r="D84" s="304">
-        <f t="shared" si="10"/>
+      <c r="D84" s="271">
+        <f t="shared" si="17"/>
         <v>46345</v>
       </c>
-      <c r="E84" s="304">
-        <f t="shared" si="11"/>
+      <c r="E84" s="271">
+        <f t="shared" si="18"/>
         <v>46346</v>
       </c>
-      <c r="F84" s="303">
-        <f t="shared" si="12"/>
+      <c r="F84" s="270">
+        <f t="shared" si="19"/>
         <v>46346</v>
       </c>
-      <c r="G84" s="303">
-        <f t="shared" si="13"/>
+      <c r="G84" s="270">
+        <f t="shared" si="20"/>
         <v>46346</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="288"/>
-      <c r="B85" s="288">
+      <c r="A85" s="255"/>
+      <c r="B85" s="255">
         <v>46321</v>
       </c>
-      <c r="C85" s="290">
+      <c r="C85" s="257">
         <v>18</v>
       </c>
-      <c r="D85" s="304">
-        <f t="shared" si="10"/>
+      <c r="D85" s="271">
+        <f t="shared" si="17"/>
         <v>46345</v>
       </c>
-      <c r="E85" s="304">
-        <f t="shared" si="11"/>
+      <c r="E85" s="271">
+        <f t="shared" si="18"/>
         <v>46346</v>
       </c>
-      <c r="F85" s="303">
-        <f t="shared" si="12"/>
+      <c r="F85" s="270">
+        <f t="shared" si="19"/>
         <v>46345</v>
       </c>
-      <c r="G85" s="303">
-        <f t="shared" si="13"/>
+      <c r="G85" s="270">
+        <f t="shared" si="20"/>
         <v>46345</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="288"/>
-      <c r="B86" s="288">
+      <c r="A86" s="255"/>
+      <c r="B86" s="255">
         <v>46322</v>
       </c>
-      <c r="C86" s="290">
+      <c r="C86" s="257">
         <v>9</v>
       </c>
-      <c r="D86" s="304">
-        <f t="shared" si="10"/>
+      <c r="D86" s="271">
+        <f t="shared" si="17"/>
         <v>46335</v>
       </c>
-      <c r="E86" s="304">
-        <f t="shared" si="11"/>
+      <c r="E86" s="271">
+        <f t="shared" si="18"/>
         <v>46336</v>
       </c>
-      <c r="F86" s="303">
-        <f t="shared" si="12"/>
+      <c r="F86" s="270">
+        <f t="shared" si="19"/>
         <v>46333</v>
       </c>
-      <c r="G86" s="303">
-        <f t="shared" si="13"/>
+      <c r="G86" s="270">
+        <f t="shared" si="20"/>
         <v>46333</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="288"/>
-      <c r="B87" s="288">
+      <c r="A87" s="255"/>
+      <c r="B87" s="255">
         <v>46323</v>
       </c>
-      <c r="C87" s="290">
+      <c r="C87" s="257">
         <v>8</v>
       </c>
-      <c r="D87" s="304">
-        <f t="shared" si="10"/>
+      <c r="D87" s="271">
+        <f t="shared" si="17"/>
         <v>46335</v>
       </c>
-      <c r="E87" s="304">
-        <f t="shared" si="11"/>
+      <c r="E87" s="271">
+        <f t="shared" si="18"/>
         <v>46336</v>
       </c>
-      <c r="F87" s="303">
-        <f t="shared" si="12"/>
+      <c r="F87" s="270">
+        <f t="shared" si="19"/>
         <v>46333</v>
       </c>
-      <c r="G87" s="303">
-        <f t="shared" si="13"/>
+      <c r="G87" s="270">
+        <f t="shared" si="20"/>
         <v>46333</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="288"/>
-      <c r="B88" s="288">
+      <c r="A88" s="255"/>
+      <c r="B88" s="255">
         <v>46324</v>
       </c>
-      <c r="C88" s="290">
+      <c r="C88" s="257">
         <v>10</v>
       </c>
-      <c r="D88" s="304">
-        <f t="shared" si="10"/>
+      <c r="D88" s="271">
+        <f t="shared" si="17"/>
         <v>46338</v>
       </c>
-      <c r="E88" s="304">
-        <f t="shared" si="11"/>
+      <c r="E88" s="271">
+        <f t="shared" si="18"/>
         <v>46339</v>
       </c>
-      <c r="F88" s="303">
-        <f t="shared" si="12"/>
+      <c r="F88" s="270">
+        <f t="shared" si="19"/>
         <v>46338</v>
       </c>
-      <c r="G88" s="303">
-        <f t="shared" si="13"/>
+      <c r="G88" s="270">
+        <f t="shared" si="20"/>
         <v>46338</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="288"/>
-      <c r="B89" s="288">
+      <c r="A89" s="255"/>
+      <c r="B89" s="255">
         <v>46325</v>
       </c>
-      <c r="C89" s="290">
+      <c r="C89" s="257">
         <v>11</v>
       </c>
-      <c r="D89" s="304">
-        <f t="shared" si="10"/>
+      <c r="D89" s="271">
+        <f t="shared" si="17"/>
         <v>46342</v>
       </c>
-      <c r="E89" s="304">
-        <f t="shared" si="11"/>
+      <c r="E89" s="271">
+        <f t="shared" si="18"/>
         <v>46343</v>
       </c>
-      <c r="F89" s="303">
-        <f t="shared" si="12"/>
+      <c r="F89" s="270">
+        <f t="shared" si="19"/>
         <v>46340</v>
       </c>
-      <c r="G89" s="303">
-        <f t="shared" si="13"/>
+      <c r="G89" s="270">
+        <f t="shared" si="20"/>
         <v>46340</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="288"/>
-      <c r="B90" s="288">
+      <c r="A90" s="255"/>
+      <c r="B90" s="255">
         <v>46326</v>
       </c>
-      <c r="C90" s="290">
+      <c r="C90" s="257">
         <v>7</v>
       </c>
-      <c r="D90" s="304">
-        <f t="shared" si="10"/>
+      <c r="D90" s="271">
+        <f t="shared" si="17"/>
         <v>46336</v>
       </c>
-      <c r="E90" s="304">
-        <f t="shared" si="11"/>
+      <c r="E90" s="271">
+        <f t="shared" si="18"/>
         <v>46337</v>
       </c>
-      <c r="F90" s="303">
-        <f t="shared" si="12"/>
+      <c r="F90" s="270">
+        <f t="shared" si="19"/>
         <v>46337</v>
       </c>
-      <c r="G90" s="303">
-        <f t="shared" si="13"/>
+      <c r="G90" s="270">
+        <f t="shared" si="20"/>
         <v>46337</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="288"/>
-      <c r="B91" s="288">
+      <c r="A91" s="255"/>
+      <c r="B91" s="255">
         <v>46327</v>
       </c>
-      <c r="C91" s="290">
+      <c r="C91" s="257">
         <v>15</v>
       </c>
-      <c r="D91" s="304">
-        <f t="shared" si="10"/>
+      <c r="D91" s="271">
+        <f t="shared" si="17"/>
         <v>46346</v>
       </c>
-      <c r="E91" s="304">
-        <f t="shared" si="11"/>
+      <c r="E91" s="271">
+        <f t="shared" si="18"/>
         <v>46349</v>
       </c>
-      <c r="F91" s="303">
-        <f t="shared" si="12"/>
+      <c r="F91" s="270">
+        <f t="shared" si="19"/>
         <v>46347</v>
       </c>
-      <c r="G91" s="303">
-        <f t="shared" si="13"/>
+      <c r="G91" s="270">
+        <f t="shared" si="20"/>
         <v>46347</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="288"/>
-      <c r="B92" s="288">
+      <c r="A92" s="255"/>
+      <c r="B92" s="255">
         <v>46328</v>
       </c>
-      <c r="C92" s="290">
+      <c r="C92" s="257">
         <v>7</v>
       </c>
-      <c r="D92" s="304">
-        <f t="shared" si="10"/>
+      <c r="D92" s="271">
+        <f t="shared" si="17"/>
         <v>46337</v>
       </c>
-      <c r="E92" s="304">
-        <f t="shared" si="11"/>
+      <c r="E92" s="271">
+        <f t="shared" si="18"/>
         <v>46338</v>
       </c>
-      <c r="F92" s="303">
-        <f t="shared" si="12"/>
+      <c r="F92" s="270">
+        <f t="shared" si="19"/>
         <v>46337</v>
       </c>
-      <c r="G92" s="303">
-        <f t="shared" si="13"/>
+      <c r="G92" s="270">
+        <f t="shared" si="20"/>
         <v>46337</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="288"/>
-      <c r="B93" s="288">
+      <c r="A93" s="255"/>
+      <c r="B93" s="255">
         <v>46329</v>
       </c>
-      <c r="C93" s="290">
+      <c r="C93" s="257">
         <v>7</v>
       </c>
-      <c r="D93" s="304">
-        <f t="shared" si="10"/>
+      <c r="D93" s="271">
+        <f t="shared" si="17"/>
         <v>46338</v>
       </c>
-      <c r="E93" s="304">
-        <f t="shared" si="11"/>
+      <c r="E93" s="271">
+        <f t="shared" si="18"/>
         <v>46339</v>
       </c>
-      <c r="F93" s="303">
-        <f t="shared" si="12"/>
+      <c r="F93" s="270">
+        <f t="shared" si="19"/>
         <v>46338</v>
       </c>
-      <c r="G93" s="303">
-        <f t="shared" si="13"/>
+      <c r="G93" s="270">
+        <f t="shared" si="20"/>
         <v>46338</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="288"/>
-      <c r="B94" s="288">
+      <c r="A94" s="255"/>
+      <c r="B94" s="255">
         <v>46330</v>
       </c>
-      <c r="C94" s="290">
+      <c r="C94" s="257">
         <v>11</v>
       </c>
-      <c r="D94" s="304">
-        <f t="shared" si="10"/>
+      <c r="D94" s="271">
+        <f t="shared" si="17"/>
         <v>46345</v>
       </c>
-      <c r="E94" s="304">
-        <f t="shared" si="11"/>
+      <c r="E94" s="271">
+        <f t="shared" si="18"/>
         <v>46346</v>
       </c>
-      <c r="F94" s="303">
-        <f t="shared" si="12"/>
+      <c r="F94" s="270">
+        <f t="shared" si="19"/>
         <v>46345</v>
       </c>
-      <c r="G94" s="303">
-        <f t="shared" si="13"/>
+      <c r="G94" s="270">
+        <f t="shared" si="20"/>
         <v>46345</v>
       </c>
     </row>
@@ -32890,362 +32890,362 @@
       </c>
     </row>
     <row r="98" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="289">
+      <c r="B98" s="256">
         <v>46318</v>
       </c>
-      <c r="C98" s="311">
+      <c r="C98" s="278">
         <v>2</v>
       </c>
-      <c r="D98" s="311">
+      <c r="D98" s="278">
         <f>C98 * 30</f>
         <v>60</v>
       </c>
-      <c r="E98" s="304">
+      <c r="E98" s="271">
         <f>EDATE(B98,C98)</f>
         <v>46379</v>
       </c>
-      <c r="F98" s="304">
+      <c r="F98" s="271">
         <f>EOMONTH(B98,C98)</f>
         <v>46387</v>
       </c>
     </row>
     <row r="99" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="289">
+      <c r="B99" s="256">
         <v>46342</v>
       </c>
-      <c r="C99" s="311">
+      <c r="C99" s="278">
         <v>3</v>
       </c>
-      <c r="D99" s="311">
-        <f t="shared" ref="D99:D115" si="14">C99 * 30</f>
+      <c r="D99" s="278">
+        <f t="shared" ref="D99:D115" si="21">C99 * 30</f>
         <v>90</v>
       </c>
-      <c r="E99" s="304">
-        <f t="shared" ref="E99:E115" si="15">EDATE(B99,C99)</f>
+      <c r="E99" s="271">
+        <f t="shared" ref="E99:E115" si="22">EDATE(B99,C99)</f>
         <v>46434</v>
       </c>
-      <c r="F99" s="304">
-        <f t="shared" ref="F99:F115" si="16">EOMONTH(B99,C99)</f>
+      <c r="F99" s="271">
+        <f t="shared" ref="F99:F115" si="23">EOMONTH(B99,C99)</f>
         <v>46446</v>
       </c>
     </row>
     <row r="100" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="289">
+      <c r="B100" s="256">
         <v>46337</v>
       </c>
-      <c r="C100" s="311">
+      <c r="C100" s="278">
         <v>4</v>
       </c>
-      <c r="D100" s="311">
-        <f t="shared" si="14"/>
+      <c r="D100" s="278">
+        <f t="shared" si="21"/>
         <v>120</v>
       </c>
-      <c r="E100" s="304">
-        <f t="shared" si="15"/>
+      <c r="E100" s="271">
+        <f t="shared" si="22"/>
         <v>46457</v>
       </c>
-      <c r="F100" s="304">
-        <f t="shared" si="16"/>
+      <c r="F100" s="271">
+        <f t="shared" si="23"/>
         <v>46477</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="289">
+      <c r="B101" s="256">
         <v>46343</v>
       </c>
-      <c r="C101" s="311">
+      <c r="C101" s="278">
         <v>5</v>
       </c>
-      <c r="D101" s="311">
-        <f t="shared" si="14"/>
+      <c r="D101" s="278">
+        <f t="shared" si="21"/>
         <v>150</v>
       </c>
-      <c r="E101" s="304">
-        <f t="shared" si="15"/>
+      <c r="E101" s="271">
+        <f t="shared" si="22"/>
         <v>46494</v>
       </c>
-      <c r="F101" s="304">
-        <f t="shared" si="16"/>
+      <c r="F101" s="271">
+        <f t="shared" si="23"/>
         <v>46507</v>
       </c>
     </row>
     <row r="102" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="289">
+      <c r="B102" s="256">
         <v>46345</v>
       </c>
-      <c r="C102" s="311">
+      <c r="C102" s="278">
         <v>1</v>
       </c>
-      <c r="D102" s="311">
-        <f t="shared" si="14"/>
+      <c r="D102" s="278">
+        <f t="shared" si="21"/>
         <v>30</v>
       </c>
-      <c r="E102" s="304">
-        <f t="shared" si="15"/>
+      <c r="E102" s="271">
+        <f t="shared" si="22"/>
         <v>46375</v>
       </c>
-      <c r="F102" s="304">
-        <f t="shared" si="16"/>
+      <c r="F102" s="271">
+        <f t="shared" si="23"/>
         <v>46387</v>
       </c>
     </row>
     <row r="103" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="289">
+      <c r="B103" s="256">
         <v>46330</v>
       </c>
-      <c r="C103" s="311">
+      <c r="C103" s="278">
         <v>2</v>
       </c>
-      <c r="D103" s="311">
-        <f t="shared" si="14"/>
+      <c r="D103" s="278">
+        <f t="shared" si="21"/>
         <v>60</v>
       </c>
-      <c r="E103" s="304">
-        <f t="shared" si="15"/>
+      <c r="E103" s="271">
+        <f t="shared" si="22"/>
         <v>46391</v>
       </c>
-      <c r="F103" s="304">
-        <f t="shared" si="16"/>
+      <c r="F103" s="271">
+        <f t="shared" si="23"/>
         <v>46418</v>
       </c>
     </row>
     <row r="104" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="289">
+      <c r="B104" s="256">
         <v>46330</v>
       </c>
-      <c r="C104" s="311">
+      <c r="C104" s="278">
         <v>4</v>
       </c>
-      <c r="D104" s="311">
-        <f t="shared" si="14"/>
+      <c r="D104" s="278">
+        <f t="shared" si="21"/>
         <v>120</v>
       </c>
-      <c r="E104" s="304">
-        <f t="shared" si="15"/>
+      <c r="E104" s="271">
+        <f t="shared" si="22"/>
         <v>46450</v>
       </c>
-      <c r="F104" s="304">
-        <f t="shared" si="16"/>
+      <c r="F104" s="271">
+        <f t="shared" si="23"/>
         <v>46477</v>
       </c>
     </row>
     <row r="105" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="289">
+      <c r="B105" s="256">
         <v>46346</v>
       </c>
-      <c r="C105" s="311">
+      <c r="C105" s="278">
         <v>6</v>
       </c>
-      <c r="D105" s="311">
-        <f t="shared" si="14"/>
+      <c r="D105" s="278">
+        <f t="shared" si="21"/>
         <v>180</v>
       </c>
-      <c r="E105" s="304">
-        <f t="shared" si="15"/>
+      <c r="E105" s="271">
+        <f t="shared" si="22"/>
         <v>46527</v>
       </c>
-      <c r="F105" s="304">
-        <f t="shared" si="16"/>
+      <c r="F105" s="271">
+        <f t="shared" si="23"/>
         <v>46538</v>
       </c>
     </row>
     <row r="106" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="289">
+      <c r="B106" s="256">
         <v>46346</v>
       </c>
-      <c r="C106" s="311">
+      <c r="C106" s="278">
         <v>2</v>
       </c>
-      <c r="D106" s="311">
-        <f t="shared" si="14"/>
+      <c r="D106" s="278">
+        <f t="shared" si="21"/>
         <v>60</v>
       </c>
-      <c r="E106" s="304">
-        <f t="shared" si="15"/>
+      <c r="E106" s="271">
+        <f t="shared" si="22"/>
         <v>46407</v>
       </c>
-      <c r="F106" s="304">
-        <f t="shared" si="16"/>
+      <c r="F106" s="271">
+        <f t="shared" si="23"/>
         <v>46418</v>
       </c>
     </row>
     <row r="107" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="289">
+      <c r="B107" s="256">
         <v>46336</v>
       </c>
-      <c r="C107" s="311">
+      <c r="C107" s="278">
         <v>3</v>
       </c>
-      <c r="D107" s="311">
-        <f t="shared" si="14"/>
+      <c r="D107" s="278">
+        <f t="shared" si="21"/>
         <v>90</v>
       </c>
-      <c r="E107" s="304">
-        <f t="shared" si="15"/>
+      <c r="E107" s="271">
+        <f t="shared" si="22"/>
         <v>46428</v>
       </c>
-      <c r="F107" s="304">
-        <f t="shared" si="16"/>
+      <c r="F107" s="271">
+        <f t="shared" si="23"/>
         <v>46446</v>
       </c>
     </row>
     <row r="108" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="289">
+      <c r="B108" s="256">
         <v>46336</v>
       </c>
-      <c r="C108" s="311">
+      <c r="C108" s="278">
         <v>4</v>
       </c>
-      <c r="D108" s="311">
-        <f t="shared" si="14"/>
+      <c r="D108" s="278">
+        <f t="shared" si="21"/>
         <v>120</v>
       </c>
-      <c r="E108" s="304">
-        <f t="shared" si="15"/>
+      <c r="E108" s="271">
+        <f t="shared" si="22"/>
         <v>46456</v>
       </c>
-      <c r="F108" s="304">
-        <f t="shared" si="16"/>
+      <c r="F108" s="271">
+        <f t="shared" si="23"/>
         <v>46477</v>
       </c>
     </row>
     <row r="109" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B109" s="289">
+      <c r="B109" s="256">
         <v>46339</v>
       </c>
-      <c r="C109" s="311">
+      <c r="C109" s="278">
         <v>5</v>
       </c>
-      <c r="D109" s="311">
-        <f t="shared" si="14"/>
+      <c r="D109" s="278">
+        <f t="shared" si="21"/>
         <v>150</v>
       </c>
-      <c r="E109" s="304">
-        <f t="shared" si="15"/>
+      <c r="E109" s="271">
+        <f t="shared" si="22"/>
         <v>46490</v>
       </c>
-      <c r="F109" s="304">
-        <f t="shared" si="16"/>
+      <c r="F109" s="271">
+        <f t="shared" si="23"/>
         <v>46507</v>
       </c>
     </row>
     <row r="110" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B110" s="289">
+      <c r="B110" s="256">
         <v>46343</v>
       </c>
-      <c r="C110" s="311">
+      <c r="C110" s="278">
         <v>6</v>
       </c>
-      <c r="D110" s="311">
-        <f t="shared" si="14"/>
+      <c r="D110" s="278">
+        <f t="shared" si="21"/>
         <v>180</v>
       </c>
-      <c r="E110" s="304">
-        <f t="shared" si="15"/>
+      <c r="E110" s="271">
+        <f t="shared" si="22"/>
         <v>46524</v>
       </c>
-      <c r="F110" s="304">
-        <f t="shared" si="16"/>
+      <c r="F110" s="271">
+        <f t="shared" si="23"/>
         <v>46538</v>
       </c>
     </row>
     <row r="111" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B111" s="289">
+      <c r="B111" s="256">
         <v>46337</v>
       </c>
-      <c r="C111" s="311">
+      <c r="C111" s="278">
         <v>8</v>
       </c>
-      <c r="D111" s="311">
-        <f t="shared" si="14"/>
+      <c r="D111" s="278">
+        <f t="shared" si="21"/>
         <v>240</v>
       </c>
-      <c r="E111" s="304">
-        <f t="shared" si="15"/>
+      <c r="E111" s="271">
+        <f t="shared" si="22"/>
         <v>46579</v>
       </c>
-      <c r="F111" s="304">
-        <f t="shared" si="16"/>
+      <c r="F111" s="271">
+        <f t="shared" si="23"/>
         <v>46599</v>
       </c>
     </row>
     <row r="112" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="289">
+      <c r="B112" s="256">
         <v>46349</v>
       </c>
-      <c r="C112" s="311">
+      <c r="C112" s="278">
         <v>7</v>
       </c>
-      <c r="D112" s="311">
-        <f t="shared" si="14"/>
+      <c r="D112" s="278">
+        <f t="shared" si="21"/>
         <v>210</v>
       </c>
-      <c r="E112" s="304">
-        <f t="shared" si="15"/>
+      <c r="E112" s="271">
+        <f t="shared" si="22"/>
         <v>46561</v>
       </c>
-      <c r="F112" s="304">
-        <f t="shared" si="16"/>
+      <c r="F112" s="271">
+        <f t="shared" si="23"/>
         <v>46568</v>
       </c>
     </row>
     <row r="113" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="289">
+      <c r="B113" s="256">
         <v>46338</v>
       </c>
-      <c r="C113" s="311">
+      <c r="C113" s="278">
         <v>9</v>
       </c>
-      <c r="D113" s="311">
-        <f t="shared" si="14"/>
+      <c r="D113" s="278">
+        <f t="shared" si="21"/>
         <v>270</v>
       </c>
-      <c r="E113" s="304">
-        <f t="shared" si="15"/>
+      <c r="E113" s="271">
+        <f t="shared" si="22"/>
         <v>46611</v>
       </c>
-      <c r="F113" s="304">
-        <f t="shared" si="16"/>
+      <c r="F113" s="271">
+        <f t="shared" si="23"/>
         <v>46630</v>
       </c>
     </row>
     <row r="114" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B114" s="289">
+      <c r="B114" s="256">
         <v>46339</v>
       </c>
-      <c r="C114" s="311">
+      <c r="C114" s="278">
         <v>10</v>
       </c>
-      <c r="D114" s="311">
-        <f t="shared" si="14"/>
+      <c r="D114" s="278">
+        <f t="shared" si="21"/>
         <v>300</v>
       </c>
-      <c r="E114" s="304">
-        <f t="shared" si="15"/>
+      <c r="E114" s="271">
+        <f t="shared" si="22"/>
         <v>46643</v>
       </c>
-      <c r="F114" s="304">
-        <f t="shared" si="16"/>
+      <c r="F114" s="271">
+        <f t="shared" si="23"/>
         <v>46660</v>
       </c>
     </row>
     <row r="115" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B115" s="289">
+      <c r="B115" s="256">
         <v>46346</v>
       </c>
-      <c r="C115" s="311">
+      <c r="C115" s="278">
         <v>11</v>
       </c>
-      <c r="D115" s="311">
-        <f t="shared" si="14"/>
+      <c r="D115" s="278">
+        <f t="shared" si="21"/>
         <v>330</v>
       </c>
-      <c r="E115" s="304">
-        <f t="shared" si="15"/>
+      <c r="E115" s="271">
+        <f t="shared" si="22"/>
         <v>46680</v>
       </c>
-      <c r="F115" s="304">
-        <f t="shared" si="16"/>
+      <c r="F115" s="271">
+        <f t="shared" si="23"/>
         <v>46691</v>
       </c>
     </row>
@@ -33265,37 +33265,37 @@
       </c>
     </row>
     <row r="119" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B119" s="325">
+      <c r="B119" s="292">
         <v>38295</v>
       </c>
-      <c r="C119" s="324" t="str">
+      <c r="C119" s="291" t="str">
         <f ca="1">TEXT(NOW(),"MM-DD-YYYY")</f>
-        <v>10-18-2026</v>
-      </c>
-      <c r="D119" s="326">
+        <v>10-19-2026</v>
+      </c>
+      <c r="D119" s="293">
         <f ca="1">DATEDIF(B119,C119,"Y")</f>
         <v>21</v>
       </c>
-      <c r="E119" s="326">
+      <c r="E119" s="293">
         <f ca="1">YEARFRAC(B119,C119)</f>
-        <v>21.955555555555556</v>
+        <v>21.958333333333332</v>
       </c>
     </row>
     <row r="120" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="286">
+      <c r="B120" s="253">
         <v>38671</v>
       </c>
-      <c r="C120" s="324" t="str">
+      <c r="C120" s="291" t="str">
         <f ca="1">TEXT(NOW(),"MM-DD-YYYY")</f>
-        <v>10-18-2026</v>
-      </c>
-      <c r="D120" s="326">
+        <v>10-19-2026</v>
+      </c>
+      <c r="D120" s="293">
         <f ca="1">DATEDIF(B120,C120,"Y")</f>
         <v>20</v>
       </c>
-      <c r="E120" s="326">
+      <c r="E120" s="293">
         <f ca="1">YEARFRAC(B120,C120)</f>
-        <v>20.925000000000001</v>
+        <v>20.927777777777777</v>
       </c>
     </row>
   </sheetData>
@@ -35758,11 +35758,11 @@
       </c>
       <c r="D2" s="25">
         <f t="shared" ref="C2:F15" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="E2" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="F2" s="25"/>
       <c r="G2" s="28">
@@ -35784,16 +35784,16 @@
       </c>
       <c r="C3" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D3" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="E3" s="25"/>
       <c r="F3" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G3" s="28">
         <f t="shared" ref="G3:G15" ca="1" si="1">COUNT(C3:F3)</f>
@@ -35815,11 +35815,11 @@
       <c r="C4" s="25"/>
       <c r="D4" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E4" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="28">
@@ -35841,16 +35841,16 @@
       </c>
       <c r="C5" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="D5" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G5" s="28">
         <f t="shared" ca="1" si="1"/>
@@ -35871,16 +35871,16 @@
       </c>
       <c r="C6" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="D6" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G6" s="28">
         <f t="shared" ca="1" si="1"/>
@@ -35902,15 +35902,15 @@
       <c r="C7" s="25"/>
       <c r="D7" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="E7" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F7" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="G7" s="28">
         <f t="shared" ca="1" si="1"/>
@@ -35931,7 +35931,7 @@
       </c>
       <c r="C8" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D8" s="25" t="s">
         <v>468</v>
@@ -35941,7 +35941,7 @@
       </c>
       <c r="F8" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="G8" s="28">
         <f t="shared" ca="1" si="1"/>
@@ -35962,19 +35962,19 @@
       </c>
       <c r="C9" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D9" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="E9" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F9" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G9" s="28">
         <f t="shared" ca="1" si="1"/>
@@ -35995,12 +35995,12 @@
       </c>
       <c r="C10" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F10" s="25"/>
       <c r="G10" s="28">
@@ -36022,19 +36022,19 @@
       </c>
       <c r="C11" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="D11" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="E11" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F11" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G11" s="28">
         <f t="shared" ca="1" si="1"/>
@@ -36055,15 +36055,15 @@
       </c>
       <c r="C12" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D12" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="E12" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F12" s="25"/>
       <c r="G12" s="28">
@@ -36085,16 +36085,16 @@
       </c>
       <c r="C13" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D13" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E13" s="25"/>
       <c r="F13" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="G13" s="28">
         <f t="shared" ca="1" si="1"/>
@@ -36115,18 +36115,18 @@
       </c>
       <c r="C14" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="D14" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>468</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="G14" s="28">
         <f t="shared" ca="1" si="1"/>
@@ -36151,7 +36151,7 @@
       <c r="D15" s="27"/>
       <c r="E15" s="27">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>468</v>
@@ -40588,54 +40588,54 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:E51">
-    <cfRule type="cellIs" dxfId="43" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="44" operator="equal">
       <formula>20000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="45" operator="between">
+    <cfRule type="cellIs" dxfId="58" priority="45" operator="between">
       <formula>50000</formula>
       <formula>100000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="46" operator="between">
+    <cfRule type="cellIs" dxfId="57" priority="46" operator="between">
       <formula>"Rs. 65,984"</formula>
       <formula>"Rs. 121,395"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="47" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="47" operator="lessThan">
       <formula>93689</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="48" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="55" priority="48" operator="greaterThan">
       <formula>93689</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="49" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="49" operator="greaterThan">
       <formula>"Rs. 93,689"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B53">
-    <cfRule type="containsText" dxfId="37" priority="43" operator="containsText" text="Ayesha khan">
+    <cfRule type="containsText" dxfId="53" priority="43" operator="containsText" text="Ayesha khan">
       <formula>NOT(ISERROR(SEARCH("Ayesha khan",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A53">
-    <cfRule type="timePeriod" dxfId="36" priority="41" timePeriod="yesterday">
+    <cfRule type="timePeriod" dxfId="52" priority="41" timePeriod="yesterday">
       <formula>FLOOR(A3,1)=TODAY()-1</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="35" priority="42" timePeriod="yesterday">
+    <cfRule type="timePeriod" dxfId="51" priority="42" timePeriod="yesterday">
       <formula>FLOOR(A3,1)=TODAY()-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A53">
-    <cfRule type="timePeriod" dxfId="34" priority="38" timePeriod="nextWeek">
+    <cfRule type="timePeriod" dxfId="50" priority="38" timePeriod="nextWeek">
       <formula>AND(ROUNDDOWN(A2,0)-TODAY()&gt;(7-WEEKDAY(TODAY())),ROUNDDOWN(A2,0)-TODAY()&lt;(15-WEEKDAY(TODAY())))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="33" priority="39" timePeriod="yesterday">
+    <cfRule type="timePeriod" dxfId="49" priority="39" timePeriod="yesterday">
       <formula>FLOOR(A2,1)=TODAY()-1</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="32" priority="40" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="48" priority="40" timePeriod="today">
       <formula>FLOOR(A2,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="uniqueValues" dxfId="31" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="37"/>
+    <cfRule type="uniqueValues" dxfId="47" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E55:E105">
     <cfRule type="dataBar" priority="18">
@@ -42851,13 +42851,13 @@
     </row>
     <row r="58" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="59" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C59" s="236" t="s">
+      <c r="C59" s="294" t="s">
         <v>528</v>
       </c>
-      <c r="D59" s="237"/>
-      <c r="E59" s="237"/>
-      <c r="F59" s="237"/>
-      <c r="G59" s="237"/>
+      <c r="D59" s="295"/>
+      <c r="E59" s="295"/>
+      <c r="F59" s="295"/>
+      <c r="G59" s="295"/>
       <c r="H59" s="88"/>
     </row>
     <row r="60" spans="3:8" x14ac:dyDescent="0.25">
@@ -48157,40 +48157,40 @@
     </row>
     <row r="168" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A169" s="238" t="s">
+      <c r="A169" s="296" t="s">
         <v>534</v>
       </c>
-      <c r="B169" s="239"/>
-      <c r="C169" s="239"/>
-      <c r="D169" s="239"/>
-      <c r="E169" s="239"/>
-      <c r="F169" s="239"/>
-      <c r="G169" s="239"/>
-      <c r="H169" s="239"/>
-      <c r="I169" s="239"/>
-      <c r="J169" s="239"/>
-      <c r="K169" s="239"/>
-      <c r="L169" s="239"/>
-      <c r="M169" s="239"/>
-      <c r="N169" s="239"/>
-      <c r="O169" s="240"/>
+      <c r="B169" s="297"/>
+      <c r="C169" s="297"/>
+      <c r="D169" s="297"/>
+      <c r="E169" s="297"/>
+      <c r="F169" s="297"/>
+      <c r="G169" s="297"/>
+      <c r="H169" s="297"/>
+      <c r="I169" s="297"/>
+      <c r="J169" s="297"/>
+      <c r="K169" s="297"/>
+      <c r="L169" s="297"/>
+      <c r="M169" s="297"/>
+      <c r="N169" s="297"/>
+      <c r="O169" s="298"/>
     </row>
     <row r="170" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="241"/>
-      <c r="B170" s="242"/>
-      <c r="C170" s="242"/>
-      <c r="D170" s="242"/>
-      <c r="E170" s="242"/>
-      <c r="F170" s="242"/>
-      <c r="G170" s="242"/>
-      <c r="H170" s="242"/>
-      <c r="I170" s="242"/>
-      <c r="J170" s="242"/>
-      <c r="K170" s="242"/>
-      <c r="L170" s="242"/>
-      <c r="M170" s="242"/>
-      <c r="N170" s="242"/>
-      <c r="O170" s="243"/>
+      <c r="A170" s="299"/>
+      <c r="B170" s="300"/>
+      <c r="C170" s="300"/>
+      <c r="D170" s="300"/>
+      <c r="E170" s="300"/>
+      <c r="F170" s="300"/>
+      <c r="G170" s="300"/>
+      <c r="H170" s="300"/>
+      <c r="I170" s="300"/>
+      <c r="J170" s="300"/>
+      <c r="K170" s="300"/>
+      <c r="L170" s="300"/>
+      <c r="M170" s="300"/>
+      <c r="N170" s="300"/>
+      <c r="O170" s="301"/>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="112"/>
